--- a/research/traditional_assets/database/data/philippines/philippines_semiconductor_equip.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_semiconductor_equip.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1810845655394924</v>
+        <v>0.1806656041256437</v>
       </c>
       <c r="C2">
-        <v>44.78320382298092</v>
+        <v>44.35981499856916</v>
       </c>
       <c r="D2">
-        <v>29.68320382298091</v>
+        <v>29.72481499856917</v>
       </c>
       <c r="E2">
-        <v>-31.7</v>
+        <v>-31.235</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.465</v>
       </c>
       <c r="G2">
         <v>15.1</v>
@@ -1445,28 +1445,28 @@
         <v>17.196</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0233895</v>
       </c>
       <c r="N2">
-        <v>17.196</v>
+        <v>17.1726105</v>
       </c>
       <c r="O2">
-        <v>4.299</v>
+        <v>4.293152625</v>
       </c>
       <c r="P2">
-        <v>12.897</v>
+        <v>12.879457875</v>
       </c>
       <c r="Q2">
-        <v>12.951</v>
+        <v>12.933457875</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1810845655394924</v>
+        <v>0.1821094486117613</v>
       </c>
       <c r="T2">
-        <v>1.968555267829297</v>
+        <v>1.983468565312853</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>735.2016930674021</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1806656041256437</v>
+        <v>0.180246642711795</v>
       </c>
       <c r="C3">
-        <v>44.35981499856916</v>
+        <v>43.93654300255827</v>
       </c>
       <c r="D3">
-        <v>29.72481499856917</v>
+        <v>29.76654300255827</v>
       </c>
       <c r="E3">
-        <v>-31.235</v>
+        <v>-30.77</v>
       </c>
       <c r="F3">
-        <v>0.465</v>
+        <v>0.93</v>
       </c>
       <c r="G3">
         <v>15.1</v>
@@ -1527,28 +1527,28 @@
         <v>17.196</v>
       </c>
       <c r="M3">
-        <v>0.0233895</v>
+        <v>0.046779</v>
       </c>
       <c r="N3">
-        <v>17.1726105</v>
+        <v>17.149221</v>
       </c>
       <c r="O3">
-        <v>4.293152625</v>
+        <v>4.28730525</v>
       </c>
       <c r="P3">
-        <v>12.879457875</v>
+        <v>12.86191575</v>
       </c>
       <c r="Q3">
-        <v>12.933457875</v>
+        <v>12.91591575</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1821094486117613</v>
+        <v>0.1831552476650969</v>
       </c>
       <c r="T3">
-        <v>1.983468565312853</v>
+        <v>1.998686215806277</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>735.2016930674021</v>
+        <v>367.600846533701</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.180246642711795</v>
+        <v>0.1798276812979462</v>
       </c>
       <c r="C4">
-        <v>43.93654300255827</v>
+        <v>43.51338832765465</v>
       </c>
       <c r="D4">
-        <v>29.76654300255827</v>
+        <v>29.80838832765465</v>
       </c>
       <c r="E4">
-        <v>-30.77</v>
+        <v>-30.305</v>
       </c>
       <c r="F4">
-        <v>0.93</v>
+        <v>1.395</v>
       </c>
       <c r="G4">
         <v>15.1</v>
@@ -1609,28 +1609,28 @@
         <v>17.196</v>
       </c>
       <c r="M4">
-        <v>0.046779</v>
+        <v>0.07016849999999999</v>
       </c>
       <c r="N4">
-        <v>17.149221</v>
+        <v>17.1258315</v>
       </c>
       <c r="O4">
-        <v>4.28730525</v>
+        <v>4.281457875</v>
       </c>
       <c r="P4">
-        <v>12.86191575</v>
+        <v>12.844373625</v>
       </c>
       <c r="Q4">
-        <v>12.91591575</v>
+        <v>12.898373625</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1831552476650969</v>
+        <v>0.1842226095855116</v>
       </c>
       <c r="T4">
-        <v>1.998686215806277</v>
+        <v>2.014217632289255</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>367.600846533701</v>
+        <v>245.0672310224674</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1798276812979462</v>
+        <v>0.1794087198840975</v>
       </c>
       <c r="C5">
-        <v>43.51338832765465</v>
+        <v>43.09035146933921</v>
       </c>
       <c r="D5">
-        <v>29.80838832765465</v>
+        <v>29.85035146933921</v>
       </c>
       <c r="E5">
-        <v>-30.305</v>
+        <v>-29.84</v>
       </c>
       <c r="F5">
-        <v>1.395</v>
+        <v>1.86</v>
       </c>
       <c r="G5">
         <v>15.1</v>
@@ -1691,28 +1691,28 @@
         <v>17.196</v>
       </c>
       <c r="M5">
-        <v>0.07016849999999999</v>
+        <v>0.093558</v>
       </c>
       <c r="N5">
-        <v>17.1258315</v>
+        <v>17.102442</v>
       </c>
       <c r="O5">
-        <v>4.281457875</v>
+        <v>4.2756105</v>
       </c>
       <c r="P5">
-        <v>12.844373625</v>
+        <v>12.8268315</v>
       </c>
       <c r="Q5">
-        <v>12.898373625</v>
+        <v>12.8808315</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1842226095855116</v>
+        <v>0.1853122082126016</v>
       </c>
       <c r="T5">
-        <v>2.014217632289255</v>
+        <v>2.030072619948963</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>245.0672310224674</v>
+        <v>183.8004232668505</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1794087198840975</v>
+        <v>0.1789897584702488</v>
       </c>
       <c r="C6">
-        <v>43.09035146933921</v>
+        <v>42.66743292588684</v>
       </c>
       <c r="D6">
-        <v>29.85035146933921</v>
+        <v>29.89243292588684</v>
       </c>
       <c r="E6">
-        <v>-29.84</v>
+        <v>-29.375</v>
       </c>
       <c r="F6">
-        <v>1.86</v>
+        <v>2.325</v>
       </c>
       <c r="G6">
         <v>15.1</v>
@@ -1773,28 +1773,28 @@
         <v>17.196</v>
       </c>
       <c r="M6">
-        <v>0.093558</v>
+        <v>0.1169475</v>
       </c>
       <c r="N6">
-        <v>17.102442</v>
+        <v>17.0790525</v>
       </c>
       <c r="O6">
-        <v>4.2756105</v>
+        <v>4.269763125000001</v>
       </c>
       <c r="P6">
-        <v>12.8268315</v>
+        <v>12.809289375</v>
       </c>
       <c r="Q6">
-        <v>12.8808315</v>
+        <v>12.863289375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1853122082126016</v>
+        <v>0.1864247457581566</v>
       </c>
       <c r="T6">
-        <v>2.030072619948963</v>
+        <v>2.046261396822559</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>183.8004232668505</v>
+        <v>147.0403386134804</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1789897584702488</v>
+        <v>0.1785707970564</v>
       </c>
       <c r="C7">
-        <v>42.66743292588684</v>
+        <v>42.24463319838619</v>
       </c>
       <c r="D7">
-        <v>29.89243292588684</v>
+        <v>29.93463319838619</v>
       </c>
       <c r="E7">
-        <v>-29.375</v>
+        <v>-28.91</v>
       </c>
       <c r="F7">
-        <v>2.325</v>
+        <v>2.79</v>
       </c>
       <c r="G7">
         <v>15.1</v>
@@ -1855,28 +1855,28 @@
         <v>17.196</v>
       </c>
       <c r="M7">
-        <v>0.1169475</v>
+        <v>0.140337</v>
       </c>
       <c r="N7">
-        <v>17.0790525</v>
+        <v>17.055663</v>
       </c>
       <c r="O7">
-        <v>4.269763125000001</v>
+        <v>4.263915750000001</v>
       </c>
       <c r="P7">
-        <v>12.809289375</v>
+        <v>12.79174725</v>
       </c>
       <c r="Q7">
-        <v>12.863289375</v>
+        <v>12.84574725</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1864247457581566</v>
+        <v>0.1875609543153192</v>
       </c>
       <c r="T7">
-        <v>2.046261396822559</v>
+        <v>2.062794615757296</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>147.0403386134804</v>
+        <v>122.5336155112337</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1785707970564</v>
+        <v>0.1781518356425513</v>
       </c>
       <c r="C8">
-        <v>42.24463319838619</v>
+        <v>41.82195279075949</v>
       </c>
       <c r="D8">
-        <v>29.93463319838619</v>
+        <v>29.97695279075949</v>
       </c>
       <c r="E8">
-        <v>-28.91</v>
+        <v>-28.445</v>
       </c>
       <c r="F8">
-        <v>2.79</v>
+        <v>3.254999999999999</v>
       </c>
       <c r="G8">
         <v>15.1</v>
@@ -1937,28 +1937,28 @@
         <v>17.196</v>
       </c>
       <c r="M8">
-        <v>0.140337</v>
+        <v>0.1637265</v>
       </c>
       <c r="N8">
-        <v>17.055663</v>
+        <v>17.0322735</v>
       </c>
       <c r="O8">
-        <v>4.263915750000001</v>
+        <v>4.258068375000001</v>
       </c>
       <c r="P8">
-        <v>12.79174725</v>
+        <v>12.774205125</v>
       </c>
       <c r="Q8">
-        <v>12.84574725</v>
+        <v>12.828205125</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1875609543153192</v>
+        <v>0.1887215974651089</v>
       </c>
       <c r="T8">
-        <v>2.062794615757296</v>
+        <v>2.079683387787403</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>122.5336155112337</v>
+        <v>105.0288132953432</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1781518356425513</v>
+        <v>0.1777328742287026</v>
       </c>
       <c r="C9">
-        <v>41.82195279075949</v>
+        <v>41.3993922097827</v>
       </c>
       <c r="D9">
-        <v>29.97695279075949</v>
+        <v>30.0193922097827</v>
       </c>
       <c r="E9">
-        <v>-28.445</v>
+        <v>-27.98</v>
       </c>
       <c r="F9">
-        <v>3.255</v>
+        <v>3.72</v>
       </c>
       <c r="G9">
         <v>15.1</v>
@@ -2019,28 +2019,28 @@
         <v>17.196</v>
       </c>
       <c r="M9">
-        <v>0.1637265</v>
+        <v>0.187116</v>
       </c>
       <c r="N9">
-        <v>17.0322735</v>
+        <v>17.008884</v>
       </c>
       <c r="O9">
-        <v>4.258068375000001</v>
+        <v>4.252221</v>
       </c>
       <c r="P9">
-        <v>12.774205125</v>
+        <v>12.756663</v>
       </c>
       <c r="Q9">
-        <v>12.828205125</v>
+        <v>12.810663</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1887215974651089</v>
+        <v>0.1899074719877202</v>
       </c>
       <c r="T9">
-        <v>2.079683387787403</v>
+        <v>2.096939307035556</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>105.0288132953432</v>
+        <v>91.90021163342526</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1777328742287026</v>
+        <v>0.1773139128148538</v>
       </c>
       <c r="C10">
-        <v>41.3993922097827</v>
+        <v>40.97695196510566</v>
       </c>
       <c r="D10">
-        <v>30.0193922097827</v>
+        <v>30.06195196510567</v>
       </c>
       <c r="E10">
-        <v>-27.98</v>
+        <v>-27.515</v>
       </c>
       <c r="F10">
-        <v>3.72</v>
+        <v>4.185</v>
       </c>
       <c r="G10">
         <v>15.1</v>
@@ -2101,28 +2101,28 @@
         <v>17.196</v>
       </c>
       <c r="M10">
-        <v>0.187116</v>
+        <v>0.2105055</v>
       </c>
       <c r="N10">
-        <v>17.008884</v>
+        <v>16.9854945</v>
       </c>
       <c r="O10">
-        <v>4.252221</v>
+        <v>4.246373625</v>
       </c>
       <c r="P10">
-        <v>12.756663</v>
+        <v>12.739120875</v>
       </c>
       <c r="Q10">
-        <v>12.810663</v>
+        <v>12.793120875</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1899074719877202</v>
+        <v>0.1911194096866526</v>
       </c>
       <c r="T10">
-        <v>2.096939307035556</v>
+        <v>2.114574477256196</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>91.90021163342526</v>
+        <v>81.68907700748913</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1773139128148538</v>
+        <v>0.1768949514010051</v>
       </c>
       <c r="C11">
-        <v>40.97695196510566</v>
+        <v>40.55463256927254</v>
       </c>
       <c r="D11">
-        <v>30.06195196510567</v>
+        <v>30.10463256927254</v>
       </c>
       <c r="E11">
-        <v>-27.515</v>
+        <v>-27.05</v>
       </c>
       <c r="F11">
-        <v>4.185</v>
+        <v>4.649999999999999</v>
       </c>
       <c r="G11">
         <v>15.1</v>
@@ -2183,28 +2183,28 @@
         <v>17.196</v>
       </c>
       <c r="M11">
-        <v>0.2105055</v>
+        <v>0.233895</v>
       </c>
       <c r="N11">
-        <v>16.9854945</v>
+        <v>16.962105</v>
       </c>
       <c r="O11">
-        <v>4.246373625</v>
+        <v>4.24052625</v>
       </c>
       <c r="P11">
-        <v>12.739120875</v>
+        <v>12.72157875</v>
       </c>
       <c r="Q11">
-        <v>12.793120875</v>
+        <v>12.77557875</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1911194096866526</v>
+        <v>0.1923582793344501</v>
       </c>
       <c r="T11">
-        <v>2.114574477256196</v>
+        <v>2.132601540148405</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>81.68907700748913</v>
+        <v>73.52016930674021</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1768949514010051</v>
+        <v>0.1764759899871564</v>
       </c>
       <c r="C12">
-        <v>40.55463256927254</v>
+        <v>40.13243453774237</v>
       </c>
       <c r="D12">
-        <v>30.10463256927254</v>
+        <v>30.14743453774237</v>
       </c>
       <c r="E12">
-        <v>-27.05</v>
+        <v>-26.585</v>
       </c>
       <c r="F12">
-        <v>4.65</v>
+        <v>5.115</v>
       </c>
       <c r="G12">
         <v>15.1</v>
@@ -2265,28 +2265,28 @@
         <v>17.196</v>
       </c>
       <c r="M12">
-        <v>0.233895</v>
+        <v>0.2572845</v>
       </c>
       <c r="N12">
-        <v>16.962105</v>
+        <v>16.9387155</v>
       </c>
       <c r="O12">
-        <v>4.24052625</v>
+        <v>4.234678875</v>
       </c>
       <c r="P12">
-        <v>12.72157875</v>
+        <v>12.704036625</v>
       </c>
       <c r="Q12">
-        <v>12.77557875</v>
+        <v>12.758036625</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1923582793344501</v>
+        <v>0.1936249887496139</v>
       </c>
       <c r="T12">
-        <v>2.132601540148405</v>
+        <v>2.151033705577519</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>73.5201693067402</v>
+        <v>66.83651755158202</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1764759899871564</v>
+        <v>0.1760570285733077</v>
       </c>
       <c r="C13">
-        <v>40.13243453774237</v>
+        <v>39.71035838890986</v>
       </c>
       <c r="D13">
-        <v>30.14743453774237</v>
+        <v>30.19035838890986</v>
       </c>
       <c r="E13">
-        <v>-26.585</v>
+        <v>-26.12</v>
       </c>
       <c r="F13">
-        <v>5.115</v>
+        <v>5.58</v>
       </c>
       <c r="G13">
         <v>15.1</v>
@@ -2347,28 +2347,28 @@
         <v>17.196</v>
       </c>
       <c r="M13">
-        <v>0.2572845</v>
+        <v>0.280674</v>
       </c>
       <c r="N13">
-        <v>16.9387155</v>
+        <v>16.915326</v>
       </c>
       <c r="O13">
-        <v>4.234678875</v>
+        <v>4.2288315</v>
       </c>
       <c r="P13">
-        <v>12.704036625</v>
+        <v>12.6864945</v>
       </c>
       <c r="Q13">
-        <v>12.758036625</v>
+        <v>12.7404945</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1936249887496139</v>
+        <v>0.1949204870151223</v>
       </c>
       <c r="T13">
-        <v>2.151033705577519</v>
+        <v>2.169884783857294</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>66.83651755158202</v>
+        <v>61.26680775561685</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1760570285733077</v>
+        <v>0.1756380671594589</v>
       </c>
       <c r="C14">
-        <v>39.71035838890986</v>
+        <v>39.28840464412624</v>
       </c>
       <c r="D14">
-        <v>30.19035838890986</v>
+        <v>30.23340464412624</v>
       </c>
       <c r="E14">
-        <v>-26.12</v>
+        <v>-25.655</v>
       </c>
       <c r="F14">
-        <v>5.58</v>
+        <v>6.045</v>
       </c>
       <c r="G14">
         <v>15.1</v>
@@ -2429,28 +2429,28 @@
         <v>17.196</v>
       </c>
       <c r="M14">
-        <v>0.280674</v>
+        <v>0.3040635</v>
       </c>
       <c r="N14">
-        <v>16.915326</v>
+        <v>16.8919365</v>
       </c>
       <c r="O14">
-        <v>4.2288315</v>
+        <v>4.222984125</v>
       </c>
       <c r="P14">
-        <v>12.6864945</v>
+        <v>12.668952375</v>
       </c>
       <c r="Q14">
-        <v>12.7404945</v>
+        <v>12.722952375</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1949204870151223</v>
+        <v>0.1962457668499528</v>
       </c>
       <c r="T14">
-        <v>2.169884783857294</v>
+        <v>2.189169220258443</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>61.26680775561685</v>
+        <v>56.55397638980016</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1756380671594589</v>
+        <v>0.1752191057456102</v>
       </c>
       <c r="C15">
-        <v>39.28840464412624</v>
+        <v>38.86657382772044</v>
       </c>
       <c r="D15">
-        <v>30.23340464412624</v>
+        <v>30.27657382772044</v>
       </c>
       <c r="E15">
-        <v>-25.655</v>
+        <v>-25.19</v>
       </c>
       <c r="F15">
-        <v>6.045</v>
+        <v>6.510000000000001</v>
       </c>
       <c r="G15">
         <v>15.1</v>
@@ -2511,28 +2511,28 @@
         <v>17.196</v>
       </c>
       <c r="M15">
-        <v>0.3040635</v>
+        <v>0.327453</v>
       </c>
       <c r="N15">
-        <v>16.8919365</v>
+        <v>16.868547</v>
       </c>
       <c r="O15">
-        <v>4.222984125</v>
+        <v>4.217136750000001</v>
       </c>
       <c r="P15">
-        <v>12.668952375</v>
+        <v>12.65141025</v>
       </c>
       <c r="Q15">
-        <v>12.722952375</v>
+        <v>12.70541025</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1962457668499528</v>
+        <v>0.1976018671460583</v>
       </c>
       <c r="T15">
-        <v>2.189169220258443</v>
+        <v>2.208902131924735</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>56.55397638980016</v>
+        <v>52.51440664767158</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1752191057456102</v>
+        <v>0.1748001443317614</v>
       </c>
       <c r="C16">
-        <v>38.86657382772044</v>
+        <v>38.44486646702035</v>
       </c>
       <c r="D16">
-        <v>30.27657382772044</v>
+        <v>30.31986646702035</v>
       </c>
       <c r="E16">
-        <v>-25.19</v>
+        <v>-24.725</v>
       </c>
       <c r="F16">
-        <v>6.510000000000001</v>
+        <v>6.975000000000001</v>
       </c>
       <c r="G16">
         <v>15.1</v>
@@ -2593,28 +2593,28 @@
         <v>17.196</v>
       </c>
       <c r="M16">
-        <v>0.327453</v>
+        <v>0.3508425000000001</v>
       </c>
       <c r="N16">
-        <v>16.868547</v>
+        <v>16.8451575</v>
       </c>
       <c r="O16">
-        <v>4.217136750000001</v>
+        <v>4.211289375000001</v>
       </c>
       <c r="P16">
-        <v>12.65141025</v>
+        <v>12.633868125</v>
       </c>
       <c r="Q16">
-        <v>12.70541025</v>
+        <v>12.687868125</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1976018671460583</v>
+        <v>0.1989898756844252</v>
       </c>
       <c r="T16">
-        <v>2.208902131924735</v>
+        <v>2.22909934739494</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>52.51440664767158</v>
+        <v>49.01344620449347</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1748001443317614</v>
+        <v>0.1743811829179127</v>
       </c>
       <c r="C17">
-        <v>38.44486646702035</v>
+        <v>38.02328309237431</v>
       </c>
       <c r="D17">
-        <v>30.31986646702035</v>
+        <v>30.3632830923743</v>
       </c>
       <c r="E17">
-        <v>-24.725</v>
+        <v>-24.26</v>
       </c>
       <c r="F17">
-        <v>6.975</v>
+        <v>7.44</v>
       </c>
       <c r="G17">
         <v>15.1</v>
@@ -2675,28 +2675,28 @@
         <v>17.196</v>
       </c>
       <c r="M17">
-        <v>0.3508424999999999</v>
+        <v>0.374232</v>
       </c>
       <c r="N17">
-        <v>16.8451575</v>
+        <v>16.821768</v>
       </c>
       <c r="O17">
-        <v>4.211289375000001</v>
+        <v>4.205442000000001</v>
       </c>
       <c r="P17">
-        <v>12.633868125</v>
+        <v>12.616326</v>
       </c>
       <c r="Q17">
-        <v>12.687868125</v>
+        <v>12.670326</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1989898756844252</v>
+        <v>0.2004109320451342</v>
       </c>
       <c r="T17">
-        <v>2.22909934739494</v>
+        <v>2.249777448947768</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>49.01344620449348</v>
+        <v>45.95010581671264</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1743811829179127</v>
+        <v>0.173962221504064</v>
       </c>
       <c r="C18">
-        <v>38.02328309237431</v>
+        <v>37.60182423717269</v>
       </c>
       <c r="D18">
-        <v>30.3632830923743</v>
+        <v>30.4068242371727</v>
       </c>
       <c r="E18">
-        <v>-24.26</v>
+        <v>-23.795</v>
       </c>
       <c r="F18">
-        <v>7.44</v>
+        <v>7.905</v>
       </c>
       <c r="G18">
         <v>15.1</v>
@@ -2757,28 +2757,28 @@
         <v>17.196</v>
       </c>
       <c r="M18">
-        <v>0.374232</v>
+        <v>0.3976215</v>
       </c>
       <c r="N18">
-        <v>16.821768</v>
+        <v>16.7983785</v>
       </c>
       <c r="O18">
-        <v>4.205442000000001</v>
+        <v>4.199594625</v>
       </c>
       <c r="P18">
-        <v>12.616326</v>
+        <v>12.598783875</v>
       </c>
       <c r="Q18">
-        <v>12.670326</v>
+        <v>12.652783875</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2004109320451342</v>
+        <v>0.201866230727788</v>
       </c>
       <c r="T18">
-        <v>2.249777448947768</v>
+        <v>2.270953818007895</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>45.95010581671264</v>
+        <v>43.24715841572954</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.173962221504064</v>
+        <v>0.1735432600902153</v>
       </c>
       <c r="C19">
-        <v>37.60182423717269</v>
+        <v>37.18049043786991</v>
       </c>
       <c r="D19">
-        <v>30.4068242371727</v>
+        <v>30.4504904378699</v>
       </c>
       <c r="E19">
-        <v>-23.795</v>
+        <v>-23.33</v>
       </c>
       <c r="F19">
-        <v>7.905</v>
+        <v>8.370000000000001</v>
       </c>
       <c r="G19">
         <v>15.1</v>
@@ -2839,28 +2839,28 @@
         <v>17.196</v>
       </c>
       <c r="M19">
-        <v>0.3976215</v>
+        <v>0.421011</v>
       </c>
       <c r="N19">
-        <v>16.7983785</v>
+        <v>16.774989</v>
       </c>
       <c r="O19">
-        <v>4.199594625</v>
+        <v>4.19374725</v>
       </c>
       <c r="P19">
-        <v>12.598783875</v>
+        <v>12.58124175</v>
       </c>
       <c r="Q19">
-        <v>12.652783875</v>
+        <v>12.63524175</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.201866230727788</v>
+        <v>0.2033570245002625</v>
       </c>
       <c r="T19">
-        <v>2.270953818007895</v>
+        <v>2.292646683874365</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>43.24715841572954</v>
+        <v>40.84453850374456</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1735432600902153</v>
+        <v>0.1731242986763666</v>
       </c>
       <c r="C20">
-        <v>37.1804904378699</v>
+        <v>36.75928223400622</v>
       </c>
       <c r="D20">
-        <v>30.4504904378699</v>
+        <v>30.49428223400622</v>
       </c>
       <c r="E20">
-        <v>-23.33000000000001</v>
+        <v>-22.865</v>
       </c>
       <c r="F20">
-        <v>8.369999999999999</v>
+        <v>8.835000000000001</v>
       </c>
       <c r="G20">
         <v>15.1</v>
@@ -2921,28 +2921,28 @@
         <v>17.196</v>
       </c>
       <c r="M20">
-        <v>0.4210109999999999</v>
+        <v>0.4444005</v>
       </c>
       <c r="N20">
-        <v>16.774989</v>
+        <v>16.7515995</v>
       </c>
       <c r="O20">
-        <v>4.19374725</v>
+        <v>4.187899875</v>
       </c>
       <c r="P20">
-        <v>12.58124175</v>
+        <v>12.563699625</v>
       </c>
       <c r="Q20">
-        <v>12.63524175</v>
+        <v>12.617699625</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2033570245002625</v>
+        <v>0.2048846279955142</v>
       </c>
       <c r="T20">
-        <v>2.292646683874365</v>
+        <v>2.314875176058526</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>40.84453850374457</v>
+        <v>38.6948259509159</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1731242986763666</v>
+        <v>0.1727053372625178</v>
       </c>
       <c r="C21">
-        <v>36.75928223400622</v>
+        <v>36.33820016823017</v>
       </c>
       <c r="D21">
-        <v>30.49428223400622</v>
+        <v>30.53820016823017</v>
       </c>
       <c r="E21">
-        <v>-22.865</v>
+        <v>-22.4</v>
       </c>
       <c r="F21">
-        <v>8.835000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G21">
         <v>15.1</v>
@@ -3003,28 +3003,28 @@
         <v>17.196</v>
       </c>
       <c r="M21">
-        <v>0.4444005</v>
+        <v>0.46779</v>
       </c>
       <c r="N21">
-        <v>16.7515995</v>
+        <v>16.72821</v>
       </c>
       <c r="O21">
-        <v>4.187899875</v>
+        <v>4.1820525</v>
       </c>
       <c r="P21">
-        <v>12.563699625</v>
+        <v>12.5461575</v>
       </c>
       <c r="Q21">
-        <v>12.617699625</v>
+        <v>12.6001575</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2048846279955142</v>
+        <v>0.2064504215781473</v>
       </c>
       <c r="T21">
-        <v>2.314875176058526</v>
+        <v>2.337659380547291</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>38.6948259509159</v>
+        <v>36.7600846533701</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1727053372625178</v>
+        <v>0.172286375848669</v>
       </c>
       <c r="C22">
-        <v>36.33820016823017</v>
+        <v>35.91724478632086</v>
       </c>
       <c r="D22">
-        <v>30.53820016823017</v>
+        <v>30.58224478632086</v>
       </c>
       <c r="E22">
-        <v>-22.4</v>
+        <v>-21.935</v>
       </c>
       <c r="F22">
-        <v>9.300000000000001</v>
+        <v>9.765000000000001</v>
       </c>
       <c r="G22">
         <v>15.1</v>
@@ -3085,28 +3085,28 @@
         <v>17.196</v>
       </c>
       <c r="M22">
-        <v>0.46779</v>
+        <v>0.4911795</v>
       </c>
       <c r="N22">
-        <v>16.72821</v>
+        <v>16.7048205</v>
       </c>
       <c r="O22">
-        <v>4.1820525</v>
+        <v>4.176205125</v>
       </c>
       <c r="P22">
-        <v>12.5461575</v>
+        <v>12.528615375</v>
       </c>
       <c r="Q22">
-        <v>12.6001575</v>
+        <v>12.582615375</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2064504215781473</v>
+        <v>0.2080558555046444</v>
       </c>
       <c r="T22">
-        <v>2.337659380547291</v>
+        <v>2.361020400339569</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>36.7600846533701</v>
+        <v>35.00960443178105</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.172286375848669</v>
+        <v>0.1718674144348203</v>
       </c>
       <c r="C23">
-        <v>35.91724478632086</v>
+        <v>35.4964166372106</v>
       </c>
       <c r="D23">
-        <v>30.58224478632086</v>
+        <v>30.6264166372106</v>
       </c>
       <c r="E23">
-        <v>-21.935</v>
+        <v>-21.47</v>
       </c>
       <c r="F23">
-        <v>9.764999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G23">
         <v>15.1</v>
@@ -3167,28 +3167,28 @@
         <v>17.196</v>
       </c>
       <c r="M23">
-        <v>0.4911794999999999</v>
+        <v>0.5145689999999999</v>
       </c>
       <c r="N23">
-        <v>16.7048205</v>
+        <v>16.681431</v>
       </c>
       <c r="O23">
-        <v>4.176205125</v>
+        <v>4.17035775</v>
       </c>
       <c r="P23">
-        <v>12.528615375</v>
+        <v>12.51107325</v>
       </c>
       <c r="Q23">
-        <v>12.582615375</v>
+        <v>12.56507325</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2080558555046444</v>
+        <v>0.2097024544036158</v>
       </c>
       <c r="T23">
-        <v>2.361020400339569</v>
+        <v>2.384980420639341</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>35.00960443178106</v>
+        <v>33.418258775791</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1718674144348203</v>
+        <v>0.1714484530209716</v>
       </c>
       <c r="C24">
-        <v>35.4964166372106</v>
+        <v>35.07571627300773</v>
       </c>
       <c r="D24">
-        <v>30.6264166372106</v>
+        <v>30.67071627300773</v>
       </c>
       <c r="E24">
-        <v>-21.47</v>
+        <v>-21.005</v>
       </c>
       <c r="F24">
-        <v>10.23</v>
+        <v>10.695</v>
       </c>
       <c r="G24">
         <v>15.1</v>
@@ -3249,28 +3249,28 @@
         <v>17.196</v>
       </c>
       <c r="M24">
-        <v>0.5145689999999999</v>
+        <v>0.5379585</v>
       </c>
       <c r="N24">
-        <v>16.681431</v>
+        <v>16.6580415</v>
       </c>
       <c r="O24">
-        <v>4.17035775</v>
+        <v>4.164510375000001</v>
       </c>
       <c r="P24">
-        <v>12.51107325</v>
+        <v>12.493531125</v>
       </c>
       <c r="Q24">
-        <v>12.56507325</v>
+        <v>12.547531125</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2097024544036158</v>
+        <v>0.2113918221051579</v>
       </c>
       <c r="T24">
-        <v>2.384980420639341</v>
+        <v>2.409562779128718</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>33.418258775791</v>
+        <v>31.96529100293053</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1714484530209716</v>
+        <v>0.1710294916071229</v>
       </c>
       <c r="C25">
-        <v>35.07571627300773</v>
+        <v>34.65514424901961</v>
       </c>
       <c r="D25">
-        <v>30.67071627300773</v>
+        <v>30.71514424901961</v>
       </c>
       <c r="E25">
-        <v>-21.005</v>
+        <v>-20.54</v>
       </c>
       <c r="F25">
-        <v>10.695</v>
+        <v>11.16</v>
       </c>
       <c r="G25">
         <v>15.1</v>
@@ -3331,28 +3331,28 @@
         <v>17.196</v>
       </c>
       <c r="M25">
-        <v>0.5379585</v>
+        <v>0.561348</v>
       </c>
       <c r="N25">
-        <v>16.6580415</v>
+        <v>16.634652</v>
       </c>
       <c r="O25">
-        <v>4.164510375000001</v>
+        <v>4.158663000000001</v>
       </c>
       <c r="P25">
-        <v>12.493531125</v>
+        <v>12.475989</v>
       </c>
       <c r="Q25">
-        <v>12.547531125</v>
+        <v>12.529989</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2113918221051579</v>
+        <v>0.2131256468514775</v>
       </c>
       <c r="T25">
-        <v>2.409562779128718</v>
+        <v>2.434792041788868</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>31.96529100293053</v>
+        <v>30.63340387780843</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1710294916071229</v>
+        <v>0.1706105301932742</v>
       </c>
       <c r="C26">
-        <v>34.65514424901961</v>
+        <v>34.23470112377584</v>
       </c>
       <c r="D26">
-        <v>30.71514424901961</v>
+        <v>30.75970112377584</v>
       </c>
       <c r="E26">
-        <v>-20.54</v>
+        <v>-20.075</v>
       </c>
       <c r="F26">
-        <v>11.16</v>
+        <v>11.625</v>
       </c>
       <c r="G26">
         <v>15.1</v>
@@ -3413,28 +3413,28 @@
         <v>17.196</v>
       </c>
       <c r="M26">
-        <v>0.561348</v>
+        <v>0.5847375</v>
       </c>
       <c r="N26">
-        <v>16.634652</v>
+        <v>16.6112625</v>
       </c>
       <c r="O26">
-        <v>4.158663000000001</v>
+        <v>4.152815625000001</v>
       </c>
       <c r="P26">
-        <v>12.475989</v>
+        <v>12.458446875</v>
       </c>
       <c r="Q26">
-        <v>12.529989</v>
+        <v>12.512446875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2131256468514775</v>
+        <v>0.2149057069243655</v>
       </c>
       <c r="T26">
-        <v>2.434792041788868</v>
+        <v>2.460694084786622</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>30.63340387780843</v>
+        <v>29.40806772269609</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1706105301932742</v>
+        <v>0.1701915687794254</v>
       </c>
       <c r="C27">
-        <v>34.23470112377584</v>
+        <v>33.81438745905159</v>
       </c>
       <c r="D27">
-        <v>30.75970112377584</v>
+        <v>30.80438745905159</v>
       </c>
       <c r="E27">
-        <v>-20.075</v>
+        <v>-19.61</v>
       </c>
       <c r="F27">
-        <v>11.625</v>
+        <v>12.09</v>
       </c>
       <c r="G27">
         <v>15.1</v>
@@ -3495,28 +3495,28 @@
         <v>17.196</v>
       </c>
       <c r="M27">
-        <v>0.5847375</v>
+        <v>0.608127</v>
       </c>
       <c r="N27">
-        <v>16.6112625</v>
+        <v>16.587873</v>
       </c>
       <c r="O27">
-        <v>4.152815625000001</v>
+        <v>4.14696825</v>
       </c>
       <c r="P27">
-        <v>12.458446875</v>
+        <v>12.44090475</v>
       </c>
       <c r="Q27">
-        <v>12.512446875</v>
+        <v>12.49490475</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2149057069243655</v>
+        <v>0.2167338767289533</v>
       </c>
       <c r="T27">
-        <v>2.460694084786622</v>
+        <v>2.487296183000531</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>29.40806772269609</v>
+        <v>28.27698819490008</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1701915687794254</v>
+        <v>0.1697726073655767</v>
       </c>
       <c r="C28">
-        <v>33.81438745905159</v>
+        <v>33.39420381989134</v>
       </c>
       <c r="D28">
-        <v>30.80438745905159</v>
+        <v>30.84920381989134</v>
       </c>
       <c r="E28">
-        <v>-19.61</v>
+        <v>-19.145</v>
       </c>
       <c r="F28">
-        <v>12.09</v>
+        <v>12.555</v>
       </c>
       <c r="G28">
         <v>15.1</v>
@@ -3577,28 +3577,28 @@
         <v>17.196</v>
       </c>
       <c r="M28">
-        <v>0.608127</v>
+        <v>0.6315165</v>
       </c>
       <c r="N28">
-        <v>16.587873</v>
+        <v>16.5644835</v>
       </c>
       <c r="O28">
-        <v>4.14696825</v>
+        <v>4.141120875</v>
       </c>
       <c r="P28">
-        <v>12.44090475</v>
+        <v>12.423362625</v>
       </c>
       <c r="Q28">
-        <v>12.49490475</v>
+        <v>12.477362625</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2167338767289533</v>
+        <v>0.2186121333775023</v>
       </c>
       <c r="T28">
-        <v>2.487296183000531</v>
+        <v>2.514627105823041</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>28.27698819490008</v>
+        <v>27.22969233582971</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1697726073655767</v>
+        <v>0.1693536459517279</v>
       </c>
       <c r="C29">
-        <v>33.39420381989134</v>
+        <v>32.97415077463258</v>
       </c>
       <c r="D29">
-        <v>30.84920381989134</v>
+        <v>30.89415077463258</v>
       </c>
       <c r="E29">
-        <v>-19.145</v>
+        <v>-18.68</v>
       </c>
       <c r="F29">
-        <v>12.555</v>
+        <v>13.02</v>
       </c>
       <c r="G29">
         <v>15.1</v>
@@ -3659,28 +3659,28 @@
         <v>17.196</v>
       </c>
       <c r="M29">
-        <v>0.6315165</v>
+        <v>0.654906</v>
       </c>
       <c r="N29">
-        <v>16.5644835</v>
+        <v>16.541094</v>
       </c>
       <c r="O29">
-        <v>4.141120875</v>
+        <v>4.1352735</v>
       </c>
       <c r="P29">
-        <v>12.423362625</v>
+        <v>12.4058205</v>
       </c>
       <c r="Q29">
-        <v>12.477362625</v>
+        <v>12.4598205</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2186121333775023</v>
+        <v>0.2205425638218444</v>
       </c>
       <c r="T29">
-        <v>2.514627105823041</v>
+        <v>2.542717220946176</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>27.22969233582971</v>
+        <v>26.25720332383579</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1693536459517279</v>
+        <v>0.1689346845378792</v>
       </c>
       <c r="C30">
-        <v>32.97415077463258</v>
+        <v>32.55422889492988</v>
       </c>
       <c r="D30">
-        <v>30.89415077463258</v>
+        <v>30.93922889492988</v>
       </c>
       <c r="E30">
-        <v>-18.68</v>
+        <v>-18.215</v>
       </c>
       <c r="F30">
-        <v>13.02</v>
+        <v>13.485</v>
       </c>
       <c r="G30">
         <v>15.1</v>
@@ -3741,28 +3741,28 @@
         <v>17.196</v>
       </c>
       <c r="M30">
-        <v>0.654906</v>
+        <v>0.6782955000000001</v>
       </c>
       <c r="N30">
-        <v>16.541094</v>
+        <v>16.5177045</v>
       </c>
       <c r="O30">
-        <v>4.1352735</v>
+        <v>4.129426125</v>
       </c>
       <c r="P30">
-        <v>12.4058205</v>
+        <v>12.388278375</v>
       </c>
       <c r="Q30">
-        <v>12.4598205</v>
+        <v>12.442278375</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2205425638218444</v>
+        <v>0.2225273725885623</v>
       </c>
       <c r="T30">
-        <v>2.542717220946176</v>
+        <v>2.57159860691785</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>26.25720332383579</v>
+        <v>25.35178251956559</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1689346845378792</v>
+        <v>0.1685157231240305</v>
       </c>
       <c r="C31">
-        <v>32.55422889492988</v>
+        <v>32.13443875577914</v>
       </c>
       <c r="D31">
-        <v>30.93922889492988</v>
+        <v>30.98443875577915</v>
       </c>
       <c r="E31">
-        <v>-18.215</v>
+        <v>-17.75</v>
       </c>
       <c r="F31">
-        <v>13.485</v>
+        <v>13.95</v>
       </c>
       <c r="G31">
         <v>15.1</v>
@@ -3823,28 +3823,28 @@
         <v>17.196</v>
       </c>
       <c r="M31">
-        <v>0.6782954999999999</v>
+        <v>0.7016849999999999</v>
       </c>
       <c r="N31">
-        <v>16.5177045</v>
+        <v>16.494315</v>
       </c>
       <c r="O31">
-        <v>4.129426125</v>
+        <v>4.12357875</v>
       </c>
       <c r="P31">
-        <v>12.388278375</v>
+        <v>12.37073625</v>
       </c>
       <c r="Q31">
-        <v>12.442278375</v>
+        <v>12.42473625</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2225273725885623</v>
+        <v>0.2245688901771864</v>
       </c>
       <c r="T31">
-        <v>2.57159860691785</v>
+        <v>2.601305175345857</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>25.35178251956559</v>
+        <v>24.50672310224674</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1685157231240305</v>
+        <v>0.1680967617101818</v>
       </c>
       <c r="C32">
-        <v>32.13443875577914</v>
+        <v>31.71478093554204</v>
       </c>
       <c r="D32">
-        <v>30.98443875577915</v>
+        <v>31.02978093554204</v>
       </c>
       <c r="E32">
-        <v>-17.75</v>
+        <v>-17.285</v>
       </c>
       <c r="F32">
-        <v>13.95</v>
+        <v>14.415</v>
       </c>
       <c r="G32">
         <v>15.1</v>
@@ -3905,28 +3905,28 @@
         <v>17.196</v>
       </c>
       <c r="M32">
-        <v>0.7016849999999999</v>
+        <v>0.7250745</v>
       </c>
       <c r="N32">
-        <v>16.494315</v>
+        <v>16.4709255</v>
       </c>
       <c r="O32">
-        <v>4.12357875</v>
+        <v>4.117731375</v>
       </c>
       <c r="P32">
-        <v>12.37073625</v>
+        <v>12.353194125</v>
       </c>
       <c r="Q32">
-        <v>12.42473625</v>
+        <v>12.407194125</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2245688901771864</v>
+        <v>0.2266695821886692</v>
       </c>
       <c r="T32">
-        <v>2.601305175345857</v>
+        <v>2.6318728037283</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>24.50672310224674</v>
+        <v>23.71618364733555</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1680967617101818</v>
+        <v>0.167677800296333</v>
       </c>
       <c r="C33">
-        <v>31.71478093554204</v>
+        <v>31.29525601597063</v>
       </c>
       <c r="D33">
-        <v>31.02978093554204</v>
+        <v>31.07525601597063</v>
       </c>
       <c r="E33">
-        <v>-17.285</v>
+        <v>-16.82</v>
       </c>
       <c r="F33">
-        <v>14.415</v>
+        <v>14.88</v>
       </c>
       <c r="G33">
         <v>15.1</v>
@@ -3987,28 +3987,28 @@
         <v>17.196</v>
       </c>
       <c r="M33">
-        <v>0.7250745</v>
+        <v>0.748464</v>
       </c>
       <c r="N33">
-        <v>16.4709255</v>
+        <v>16.447536</v>
       </c>
       <c r="O33">
-        <v>4.117731375</v>
+        <v>4.111884000000001</v>
       </c>
       <c r="P33">
-        <v>12.353194125</v>
+        <v>12.335652</v>
       </c>
       <c r="Q33">
-        <v>12.407194125</v>
+        <v>12.389652</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2266695821886692</v>
+        <v>0.2288320592593133</v>
       </c>
       <c r="T33">
-        <v>2.6318728037283</v>
+        <v>2.663339480004344</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>23.71618364733555</v>
+        <v>22.97505290835632</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.167677800296333</v>
+        <v>0.1672588388824843</v>
       </c>
       <c r="C34">
-        <v>31.29525601597063</v>
+        <v>30.87586458223233</v>
       </c>
       <c r="D34">
-        <v>31.07525601597063</v>
+        <v>31.12086458223233</v>
       </c>
       <c r="E34">
-        <v>-16.82</v>
+        <v>-16.355</v>
       </c>
       <c r="F34">
-        <v>14.88</v>
+        <v>15.345</v>
       </c>
       <c r="G34">
         <v>15.1</v>
@@ -4069,28 +4069,28 @@
         <v>17.196</v>
       </c>
       <c r="M34">
-        <v>0.748464</v>
+        <v>0.7718535</v>
       </c>
       <c r="N34">
-        <v>16.447536</v>
+        <v>16.4241465</v>
       </c>
       <c r="O34">
-        <v>4.111884000000001</v>
+        <v>4.106036625000001</v>
       </c>
       <c r="P34">
-        <v>12.335652</v>
+        <v>12.318109875</v>
       </c>
       <c r="Q34">
-        <v>12.389652</v>
+        <v>12.372109875</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2288320592593133</v>
+        <v>0.2310590878843049</v>
       </c>
       <c r="T34">
-        <v>2.663339480004344</v>
+        <v>2.695745460049822</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>22.97505290835632</v>
+        <v>22.27883918386067</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1672588388824843</v>
+        <v>0.1668398774686355</v>
       </c>
       <c r="C35">
-        <v>30.87586458223233</v>
+        <v>30.45660722293491</v>
       </c>
       <c r="D35">
-        <v>31.12086458223233</v>
+        <v>31.16660722293491</v>
       </c>
       <c r="E35">
-        <v>-16.355</v>
+        <v>-15.89</v>
       </c>
       <c r="F35">
-        <v>15.345</v>
+        <v>15.81</v>
       </c>
       <c r="G35">
         <v>15.1</v>
@@ -4151,28 +4151,28 @@
         <v>17.196</v>
       </c>
       <c r="M35">
-        <v>0.7718535</v>
+        <v>0.795243</v>
       </c>
       <c r="N35">
-        <v>16.4241465</v>
+        <v>16.400757</v>
       </c>
       <c r="O35">
-        <v>4.106036625000001</v>
+        <v>4.100189250000001</v>
       </c>
       <c r="P35">
-        <v>12.318109875</v>
+        <v>12.30056775</v>
       </c>
       <c r="Q35">
-        <v>12.372109875</v>
+        <v>12.35456775</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2310590878843049</v>
+        <v>0.2333536022252054</v>
       </c>
       <c r="T35">
-        <v>2.695745460049822</v>
+        <v>2.729133439490617</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>22.27883918386067</v>
+        <v>21.62357920786477</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1668398774686355</v>
+        <v>0.1664209160547868</v>
       </c>
       <c r="C36">
-        <v>30.45660722293491</v>
+        <v>30.03748453015191</v>
       </c>
       <c r="D36">
-        <v>31.16660722293491</v>
+        <v>31.21248453015192</v>
       </c>
       <c r="E36">
-        <v>-15.89</v>
+        <v>-15.425</v>
       </c>
       <c r="F36">
-        <v>15.81</v>
+        <v>16.275</v>
       </c>
       <c r="G36">
         <v>15.1</v>
@@ -4233,28 +4233,28 @@
         <v>17.196</v>
       </c>
       <c r="M36">
-        <v>0.795243</v>
+        <v>0.8186325000000001</v>
       </c>
       <c r="N36">
-        <v>16.400757</v>
+        <v>16.3773675</v>
       </c>
       <c r="O36">
-        <v>4.100189250000001</v>
+        <v>4.094341875</v>
       </c>
       <c r="P36">
-        <v>12.30056775</v>
+        <v>12.283025625</v>
       </c>
       <c r="Q36">
-        <v>12.35456775</v>
+        <v>12.337025625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2333536022252054</v>
+        <v>0.2357187170073644</v>
       </c>
       <c r="T36">
-        <v>2.729133439490617</v>
+        <v>2.763548741375745</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>21.62357920786477</v>
+        <v>21.00576265906863</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1664209160547868</v>
+        <v>0.1660019546409381</v>
       </c>
       <c r="C37">
-        <v>30.03748453015191</v>
+        <v>29.61849709944813</v>
       </c>
       <c r="D37">
-        <v>31.21248453015192</v>
+        <v>31.25849709944813</v>
       </c>
       <c r="E37">
-        <v>-15.425</v>
+        <v>-14.96</v>
       </c>
       <c r="F37">
-        <v>16.275</v>
+        <v>16.74</v>
       </c>
       <c r="G37">
         <v>15.1</v>
@@ -4315,28 +4315,28 @@
         <v>17.196</v>
       </c>
       <c r="M37">
-        <v>0.8186325000000001</v>
+        <v>0.842022</v>
       </c>
       <c r="N37">
-        <v>16.3773675</v>
+        <v>16.353978</v>
       </c>
       <c r="O37">
-        <v>4.094341875</v>
+        <v>4.0884945</v>
       </c>
       <c r="P37">
-        <v>12.283025625</v>
+        <v>12.2654835</v>
       </c>
       <c r="Q37">
-        <v>12.337025625</v>
+        <v>12.3194835</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2357187170073644</v>
+        <v>0.2381577416264658</v>
       </c>
       <c r="T37">
-        <v>2.763548741375745</v>
+        <v>2.799039521444783</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>21.00576265906863</v>
+        <v>20.42226925187228</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1660019546409381</v>
+        <v>0.1655829932270894</v>
       </c>
       <c r="C38">
-        <v>29.61849709944812</v>
+        <v>29.19964552990539</v>
       </c>
       <c r="D38">
-        <v>31.25849709944812</v>
+        <v>31.30464552990539</v>
       </c>
       <c r="E38">
-        <v>-14.96</v>
+        <v>-14.495</v>
       </c>
       <c r="F38">
-        <v>16.74</v>
+        <v>17.205</v>
       </c>
       <c r="G38">
         <v>15.1</v>
@@ -4397,28 +4397,28 @@
         <v>17.196</v>
       </c>
       <c r="M38">
-        <v>0.8420219999999998</v>
+        <v>0.8654114999999999</v>
       </c>
       <c r="N38">
-        <v>16.353978</v>
+        <v>16.3305885</v>
       </c>
       <c r="O38">
-        <v>4.0884945</v>
+        <v>4.082647125</v>
       </c>
       <c r="P38">
-        <v>12.2654835</v>
+        <v>12.247941375</v>
       </c>
       <c r="Q38">
-        <v>12.3194835</v>
+        <v>12.301941375</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2381577416264658</v>
+        <v>0.2406741955985545</v>
       </c>
       <c r="T38">
-        <v>2.799039521444783</v>
+        <v>2.835656992944583</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>20.42226925187228</v>
+        <v>19.87031602884871</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1655829932270894</v>
+        <v>0.1651640318132407</v>
       </c>
       <c r="C39">
-        <v>29.19964552990539</v>
+        <v>28.78093042414858</v>
       </c>
       <c r="D39">
-        <v>31.30464552990539</v>
+        <v>31.35093042414858</v>
       </c>
       <c r="E39">
-        <v>-14.495</v>
+        <v>-14.03</v>
       </c>
       <c r="F39">
-        <v>17.205</v>
+        <v>17.67</v>
       </c>
       <c r="G39">
         <v>15.1</v>
@@ -4479,28 +4479,28 @@
         <v>17.196</v>
       </c>
       <c r="M39">
-        <v>0.8654114999999999</v>
+        <v>0.8888010000000001</v>
       </c>
       <c r="N39">
-        <v>16.3305885</v>
+        <v>16.307199</v>
       </c>
       <c r="O39">
-        <v>4.082647125</v>
+        <v>4.07679975</v>
       </c>
       <c r="P39">
-        <v>12.247941375</v>
+        <v>12.23039925</v>
       </c>
       <c r="Q39">
-        <v>12.301941375</v>
+        <v>12.28439925</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2406741955985545</v>
+        <v>0.2432718255052269</v>
       </c>
       <c r="T39">
-        <v>2.835656992944583</v>
+        <v>2.873455673202443</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>19.87031602884871</v>
+        <v>19.34741297545795</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1651640318132407</v>
+        <v>0.1647450703993919</v>
       </c>
       <c r="C40">
-        <v>28.78093042414858</v>
+        <v>28.36235238837188</v>
       </c>
       <c r="D40">
-        <v>31.35093042414858</v>
+        <v>31.39735238837188</v>
       </c>
       <c r="E40">
-        <v>-14.03</v>
+        <v>-13.565</v>
       </c>
       <c r="F40">
-        <v>17.67</v>
+        <v>18.135</v>
       </c>
       <c r="G40">
         <v>15.1</v>
@@ -4561,28 +4561,28 @@
         <v>17.196</v>
       </c>
       <c r="M40">
-        <v>0.8888010000000001</v>
+        <v>0.9121905</v>
       </c>
       <c r="N40">
-        <v>16.307199</v>
+        <v>16.2838095</v>
       </c>
       <c r="O40">
-        <v>4.07679975</v>
+        <v>4.070952375</v>
       </c>
       <c r="P40">
-        <v>12.23039925</v>
+        <v>12.212857125</v>
       </c>
       <c r="Q40">
-        <v>12.28439925</v>
+        <v>12.266857125</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2432718255052269</v>
+        <v>0.2459546236055605</v>
       </c>
       <c r="T40">
-        <v>2.873455673202443</v>
+        <v>2.912493654452362</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>19.34741297545795</v>
+        <v>18.85132546326672</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1647450703993919</v>
+        <v>0.1643261089855432</v>
       </c>
       <c r="C41">
-        <v>28.36235238837188</v>
+        <v>27.94391203236518</v>
       </c>
       <c r="D41">
-        <v>31.39735238837188</v>
+        <v>31.44391203236518</v>
       </c>
       <c r="E41">
-        <v>-13.565</v>
+        <v>-13.1</v>
       </c>
       <c r="F41">
-        <v>18.135</v>
+        <v>18.6</v>
       </c>
       <c r="G41">
         <v>15.1</v>
@@ -4643,28 +4643,28 @@
         <v>17.196</v>
       </c>
       <c r="M41">
-        <v>0.9121905</v>
+        <v>0.9355800000000001</v>
       </c>
       <c r="N41">
-        <v>16.2838095</v>
+        <v>16.26042</v>
       </c>
       <c r="O41">
-        <v>4.070952375</v>
+        <v>4.065105</v>
       </c>
       <c r="P41">
-        <v>12.212857125</v>
+        <v>12.195315</v>
       </c>
       <c r="Q41">
-        <v>12.266857125</v>
+        <v>12.249315</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2459546236055605</v>
+        <v>0.2487268483092386</v>
       </c>
       <c r="T41">
-        <v>2.912493654452362</v>
+        <v>2.952832901743946</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>18.85132546326672</v>
+        <v>18.38004232668505</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1643261089855432</v>
+        <v>0.1639071475716944</v>
       </c>
       <c r="C42">
-        <v>27.94391203236518</v>
+        <v>27.52560996954081</v>
       </c>
       <c r="D42">
-        <v>31.44391203236518</v>
+        <v>31.49060996954082</v>
       </c>
       <c r="E42">
-        <v>-13.1</v>
+        <v>-12.635</v>
       </c>
       <c r="F42">
-        <v>18.6</v>
+        <v>19.065</v>
       </c>
       <c r="G42">
         <v>15.1</v>
@@ -4725,28 +4725,28 @@
         <v>17.196</v>
       </c>
       <c r="M42">
-        <v>0.9355800000000001</v>
+        <v>0.9589695</v>
       </c>
       <c r="N42">
-        <v>16.26042</v>
+        <v>16.2370305</v>
       </c>
       <c r="O42">
-        <v>4.065105</v>
+        <v>4.059257625000001</v>
       </c>
       <c r="P42">
-        <v>12.195315</v>
+        <v>12.177772875</v>
       </c>
       <c r="Q42">
-        <v>12.249315</v>
+        <v>12.231772875</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2487268483092386</v>
+        <v>0.2515930467316855</v>
       </c>
       <c r="T42">
-        <v>2.952832901743946</v>
+        <v>2.99453958114711</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>18.38004232668505</v>
+        <v>17.93174861140005</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1639071475716944</v>
+        <v>0.1634881861578457</v>
       </c>
       <c r="C43">
-        <v>27.52560996954081</v>
+        <v>27.10744681696052</v>
       </c>
       <c r="D43">
-        <v>31.49060996954082</v>
+        <v>31.53744681696052</v>
       </c>
       <c r="E43">
-        <v>-12.635</v>
+        <v>-12.17</v>
       </c>
       <c r="F43">
-        <v>19.065</v>
+        <v>19.53</v>
       </c>
       <c r="G43">
         <v>15.1</v>
@@ -4807,28 +4807,28 @@
         <v>17.196</v>
       </c>
       <c r="M43">
-        <v>0.9589695</v>
+        <v>0.982359</v>
       </c>
       <c r="N43">
-        <v>16.2370305</v>
+        <v>16.213641</v>
       </c>
       <c r="O43">
-        <v>4.059257625000001</v>
+        <v>4.053410250000001</v>
       </c>
       <c r="P43">
-        <v>12.177772875</v>
+        <v>12.16023075</v>
       </c>
       <c r="Q43">
-        <v>12.231772875</v>
+        <v>12.21423075</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2515930467316855</v>
+        <v>0.2545580795824926</v>
       </c>
       <c r="T43">
-        <v>2.99453958114711</v>
+        <v>3.037684421909002</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>17.93174861140005</v>
+        <v>17.50480221589053</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1634881861578457</v>
+        <v>0.163069224743997</v>
       </c>
       <c r="C44">
-        <v>27.10744681696052</v>
+        <v>26.68942319536256</v>
       </c>
       <c r="D44">
-        <v>31.53744681696052</v>
+        <v>31.58442319536256</v>
       </c>
       <c r="E44">
-        <v>-12.17000000000001</v>
+        <v>-11.705</v>
       </c>
       <c r="F44">
-        <v>19.53</v>
+        <v>19.995</v>
       </c>
       <c r="G44">
         <v>15.1</v>
@@ -4889,28 +4889,28 @@
         <v>17.196</v>
       </c>
       <c r="M44">
-        <v>0.9823589999999999</v>
+        <v>1.0057485</v>
       </c>
       <c r="N44">
-        <v>16.213641</v>
+        <v>16.1902515</v>
       </c>
       <c r="O44">
-        <v>4.053410250000001</v>
+        <v>4.047562875000001</v>
       </c>
       <c r="P44">
-        <v>12.16023075</v>
+        <v>12.142688625</v>
       </c>
       <c r="Q44">
-        <v>12.21423075</v>
+        <v>12.196688625</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2545580795824926</v>
+        <v>0.2576271486736789</v>
       </c>
       <c r="T44">
-        <v>3.037684421909002</v>
+        <v>3.082343116732715</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>17.50480221589053</v>
+        <v>17.09771379226517</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.163069224743997</v>
+        <v>0.1626502633301483</v>
       </c>
       <c r="C45">
-        <v>26.68942319536256</v>
+        <v>26.27153972918923</v>
       </c>
       <c r="D45">
-        <v>31.58442319536256</v>
+        <v>31.63153972918923</v>
       </c>
       <c r="E45">
-        <v>-11.705</v>
+        <v>-11.24</v>
       </c>
       <c r="F45">
-        <v>19.995</v>
+        <v>20.46</v>
       </c>
       <c r="G45">
         <v>15.1</v>
@@ -4971,28 +4971,28 @@
         <v>17.196</v>
       </c>
       <c r="M45">
-        <v>1.0057485</v>
+        <v>1.029138</v>
       </c>
       <c r="N45">
-        <v>16.1902515</v>
+        <v>16.166862</v>
       </c>
       <c r="O45">
-        <v>4.047562875000001</v>
+        <v>4.0417155</v>
       </c>
       <c r="P45">
-        <v>12.142688625</v>
+        <v>12.1251465</v>
       </c>
       <c r="Q45">
-        <v>12.196688625</v>
+        <v>12.1791465</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2576271486736789</v>
+        <v>0.2608058273752648</v>
       </c>
       <c r="T45">
-        <v>3.082343116732715</v>
+        <v>3.128596764942991</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>17.09771379226517</v>
+        <v>16.7091293878955</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1626502633301483</v>
+        <v>0.1622313019162995</v>
       </c>
       <c r="C46">
-        <v>26.27153972918923</v>
+        <v>25.85379704661442</v>
       </c>
       <c r="D46">
-        <v>31.63153972918923</v>
+        <v>31.67879704661442</v>
       </c>
       <c r="E46">
-        <v>-11.24</v>
+        <v>-10.775</v>
       </c>
       <c r="F46">
-        <v>20.46</v>
+        <v>20.925</v>
       </c>
       <c r="G46">
         <v>15.1</v>
@@ -5053,28 +5053,28 @@
         <v>17.196</v>
       </c>
       <c r="M46">
-        <v>1.029138</v>
+        <v>1.0525275</v>
       </c>
       <c r="N46">
-        <v>16.166862</v>
+        <v>16.1434725</v>
       </c>
       <c r="O46">
-        <v>4.0417155</v>
+        <v>4.035868125</v>
       </c>
       <c r="P46">
-        <v>12.1251465</v>
+        <v>12.107604375</v>
       </c>
       <c r="Q46">
-        <v>12.1791465</v>
+        <v>12.161604375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2608058273752648</v>
+        <v>0.2641000943932719</v>
       </c>
       <c r="T46">
-        <v>3.128596764942991</v>
+        <v>3.176532363997275</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>16.7091293878955</v>
+        <v>16.33781540149782</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1622313019162995</v>
+        <v>0.1618123405024508</v>
       </c>
       <c r="C47">
-        <v>25.85379704661442</v>
+        <v>25.43619577957162</v>
       </c>
       <c r="D47">
-        <v>31.67879704661442</v>
+        <v>31.72619577957162</v>
       </c>
       <c r="E47">
-        <v>-10.775</v>
+        <v>-10.31</v>
       </c>
       <c r="F47">
-        <v>20.925</v>
+        <v>21.39</v>
       </c>
       <c r="G47">
         <v>15.1</v>
@@ -5135,28 +5135,28 @@
         <v>17.196</v>
       </c>
       <c r="M47">
-        <v>1.0525275</v>
+        <v>1.075917</v>
       </c>
       <c r="N47">
-        <v>16.1434725</v>
+        <v>16.120083</v>
       </c>
       <c r="O47">
-        <v>4.035868125</v>
+        <v>4.03002075</v>
       </c>
       <c r="P47">
-        <v>12.107604375</v>
+        <v>12.09006225</v>
       </c>
       <c r="Q47">
-        <v>12.161604375</v>
+        <v>12.14406225</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2641000943932719</v>
+        <v>0.2675163713008348</v>
       </c>
       <c r="T47">
-        <v>3.176532363997275</v>
+        <v>3.226243355609126</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>16.33781540149782</v>
+        <v>15.98264550146526</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1618123405024508</v>
+        <v>0.161393379088602</v>
       </c>
       <c r="C48">
-        <v>25.43619577957162</v>
+        <v>25.01873656378205</v>
       </c>
       <c r="D48">
-        <v>31.72619577957162</v>
+        <v>31.77373656378205</v>
       </c>
       <c r="E48">
-        <v>-10.31</v>
+        <v>-9.845000000000002</v>
       </c>
       <c r="F48">
-        <v>21.39</v>
+        <v>21.855</v>
       </c>
       <c r="G48">
         <v>15.1</v>
@@ -5217,28 +5217,28 @@
         <v>17.196</v>
       </c>
       <c r="M48">
-        <v>1.075917</v>
+        <v>1.0993065</v>
       </c>
       <c r="N48">
-        <v>16.120083</v>
+        <v>16.0966935</v>
       </c>
       <c r="O48">
-        <v>4.03002075</v>
+        <v>4.024173375</v>
       </c>
       <c r="P48">
-        <v>12.09006225</v>
+        <v>12.072520125</v>
       </c>
       <c r="Q48">
-        <v>12.14406225</v>
+        <v>12.126520125</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2675163713008348</v>
+        <v>0.2710615643181171</v>
       </c>
       <c r="T48">
-        <v>3.226243355609126</v>
+        <v>3.277830233696896</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>15.98264550146526</v>
+        <v>15.64258921420005</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.161393379088602</v>
+        <v>0.1609744176747533</v>
       </c>
       <c r="C49">
-        <v>25.01873656378205</v>
+        <v>24.60142003878308</v>
       </c>
       <c r="D49">
-        <v>31.77373656378205</v>
+        <v>31.82142003878309</v>
       </c>
       <c r="E49">
-        <v>-9.845000000000002</v>
+        <v>-9.380000000000003</v>
       </c>
       <c r="F49">
-        <v>21.855</v>
+        <v>22.32</v>
       </c>
       <c r="G49">
         <v>15.1</v>
@@ -5299,28 +5299,28 @@
         <v>17.196</v>
       </c>
       <c r="M49">
-        <v>1.0993065</v>
+        <v>1.122696</v>
       </c>
       <c r="N49">
-        <v>16.0966935</v>
+        <v>16.073304</v>
       </c>
       <c r="O49">
-        <v>4.024173375</v>
+        <v>4.018326</v>
       </c>
       <c r="P49">
-        <v>12.072520125</v>
+        <v>12.054978</v>
       </c>
       <c r="Q49">
-        <v>12.126520125</v>
+        <v>12.108978</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2710615643181171</v>
+        <v>0.2747431109129871</v>
       </c>
       <c r="T49">
-        <v>3.277830233696896</v>
+        <v>3.331401222480349</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>15.64258921420005</v>
+        <v>15.31670193890421</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1609744176747533</v>
+        <v>0.1605554562609046</v>
       </c>
       <c r="C50">
-        <v>24.60142003878309</v>
+        <v>24.18424684795695</v>
       </c>
       <c r="D50">
-        <v>31.82142003878309</v>
+        <v>31.86924684795695</v>
       </c>
       <c r="E50">
-        <v>-9.380000000000003</v>
+        <v>-8.915000000000003</v>
       </c>
       <c r="F50">
-        <v>22.32</v>
+        <v>22.785</v>
       </c>
       <c r="G50">
         <v>15.1</v>
@@ -5381,28 +5381,28 @@
         <v>17.196</v>
       </c>
       <c r="M50">
-        <v>1.122696</v>
+        <v>1.1460855</v>
       </c>
       <c r="N50">
-        <v>16.073304</v>
+        <v>16.0499145</v>
       </c>
       <c r="O50">
-        <v>4.018326</v>
+        <v>4.012478625</v>
       </c>
       <c r="P50">
-        <v>12.054978</v>
+        <v>12.037435875</v>
       </c>
       <c r="Q50">
-        <v>12.108978</v>
+        <v>12.091435875</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2747431109129871</v>
+        <v>0.2785690318841266</v>
       </c>
       <c r="T50">
-        <v>3.331401222480349</v>
+        <v>3.38707303435335</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>15.31670193890421</v>
+        <v>15.00411618504902</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1605554562609046</v>
+        <v>0.1601364948470559</v>
       </c>
       <c r="C51">
-        <v>24.18424684795695</v>
+        <v>23.76721763855961</v>
       </c>
       <c r="D51">
-        <v>31.86924684795695</v>
+        <v>31.91721763855962</v>
       </c>
       <c r="E51">
-        <v>-8.915000000000003</v>
+        <v>-8.450000000000003</v>
       </c>
       <c r="F51">
-        <v>22.785</v>
+        <v>23.25</v>
       </c>
       <c r="G51">
         <v>15.1</v>
@@ -5463,28 +5463,28 @@
         <v>17.196</v>
       </c>
       <c r="M51">
-        <v>1.1460855</v>
+        <v>1.169475</v>
       </c>
       <c r="N51">
-        <v>16.0499145</v>
+        <v>16.026525</v>
       </c>
       <c r="O51">
-        <v>4.012478625</v>
+        <v>4.006631250000001</v>
       </c>
       <c r="P51">
-        <v>12.037435875</v>
+        <v>12.01989375</v>
       </c>
       <c r="Q51">
-        <v>12.091435875</v>
+        <v>12.07389375</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2785690318841266</v>
+        <v>0.2825479896941117</v>
       </c>
       <c r="T51">
-        <v>3.38707303435335</v>
+        <v>3.444971718701271</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>15.00411618504902</v>
+        <v>14.70403386134804</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1601364948470559</v>
+        <v>0.1597175334332071</v>
       </c>
       <c r="C52">
-        <v>23.76721763855961</v>
+        <v>23.35033306175005</v>
       </c>
       <c r="D52">
-        <v>31.91721763855962</v>
+        <v>31.96533306175004</v>
       </c>
       <c r="E52">
-        <v>-8.450000000000003</v>
+        <v>-7.985000000000003</v>
       </c>
       <c r="F52">
-        <v>23.25</v>
+        <v>23.715</v>
       </c>
       <c r="G52">
         <v>15.1</v>
@@ -5545,28 +5545,28 @@
         <v>17.196</v>
       </c>
       <c r="M52">
-        <v>1.169475</v>
+        <v>1.1928645</v>
       </c>
       <c r="N52">
-        <v>16.026525</v>
+        <v>16.0031355</v>
       </c>
       <c r="O52">
-        <v>4.006631250000001</v>
+        <v>4.000783875000001</v>
       </c>
       <c r="P52">
-        <v>12.01989375</v>
+        <v>12.002351625</v>
       </c>
       <c r="Q52">
-        <v>12.07389375</v>
+        <v>12.056351625</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2825479896941117</v>
+        <v>0.2866893539453207</v>
       </c>
       <c r="T52">
-        <v>3.444971718701271</v>
+        <v>3.505233614655229</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>14.70403386134804</v>
+        <v>14.41571947190985</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1597175334332071</v>
+        <v>0.1592985720193584</v>
       </c>
       <c r="C53">
-        <v>23.35033306175005</v>
+        <v>22.93359377261963</v>
       </c>
       <c r="D53">
-        <v>31.96533306175004</v>
+        <v>32.01359377261963</v>
       </c>
       <c r="E53">
-        <v>-7.985000000000003</v>
+        <v>-7.520000000000003</v>
       </c>
       <c r="F53">
-        <v>23.715</v>
+        <v>24.18</v>
       </c>
       <c r="G53">
         <v>15.1</v>
@@ -5627,28 +5627,28 @@
         <v>17.196</v>
       </c>
       <c r="M53">
-        <v>1.1928645</v>
+        <v>1.216254</v>
       </c>
       <c r="N53">
-        <v>16.0031355</v>
+        <v>15.979746</v>
       </c>
       <c r="O53">
-        <v>4.000783875000001</v>
+        <v>3.994936500000001</v>
       </c>
       <c r="P53">
-        <v>12.002351625</v>
+        <v>11.9848095</v>
       </c>
       <c r="Q53">
-        <v>12.056351625</v>
+        <v>12.0388095</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2866893539453207</v>
+        <v>0.29100327504033</v>
       </c>
       <c r="T53">
-        <v>3.505233614655229</v>
+        <v>3.568006422940602</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>14.41571947190985</v>
+        <v>14.13849409745004</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1592985720193584</v>
+        <v>0.1588796106055097</v>
       </c>
       <c r="C54">
-        <v>22.93359377261963</v>
+        <v>22.51700043022192</v>
       </c>
       <c r="D54">
-        <v>32.01359377261963</v>
+        <v>32.06200043022192</v>
       </c>
       <c r="E54">
-        <v>-7.520000000000003</v>
+        <v>-7.055000000000003</v>
       </c>
       <c r="F54">
-        <v>24.18</v>
+        <v>24.645</v>
       </c>
       <c r="G54">
         <v>15.1</v>
@@ -5709,28 +5709,28 @@
         <v>17.196</v>
       </c>
       <c r="M54">
-        <v>1.216254</v>
+        <v>1.2396435</v>
       </c>
       <c r="N54">
-        <v>15.979746</v>
+        <v>15.9563565</v>
       </c>
       <c r="O54">
-        <v>3.994936500000001</v>
+        <v>3.989089125</v>
       </c>
       <c r="P54">
-        <v>11.9848095</v>
+        <v>11.967267375</v>
       </c>
       <c r="Q54">
-        <v>12.0388095</v>
+        <v>12.021267375</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.29100327504033</v>
+        <v>0.2955007672457653</v>
       </c>
       <c r="T54">
-        <v>3.568006422940602</v>
+        <v>3.633450414557267</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>14.13849409745004</v>
+        <v>13.87173005787551</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1588796106055097</v>
+        <v>0.1584606491916609</v>
       </c>
       <c r="C55">
-        <v>22.51700043022192</v>
+        <v>22.10055369760265</v>
       </c>
       <c r="D55">
-        <v>32.06200043022192</v>
+        <v>32.11055369760265</v>
       </c>
       <c r="E55">
-        <v>-7.055000000000003</v>
+        <v>-6.59</v>
       </c>
       <c r="F55">
-        <v>24.645</v>
+        <v>25.11</v>
       </c>
       <c r="G55">
         <v>15.1</v>
@@ -5791,28 +5791,28 @@
         <v>17.196</v>
       </c>
       <c r="M55">
-        <v>1.2396435</v>
+        <v>1.263033</v>
       </c>
       <c r="N55">
-        <v>15.9563565</v>
+        <v>15.932967</v>
       </c>
       <c r="O55">
-        <v>3.989089125</v>
+        <v>3.98324175</v>
       </c>
       <c r="P55">
-        <v>11.967267375</v>
+        <v>11.94972525</v>
       </c>
       <c r="Q55">
-        <v>12.021267375</v>
+        <v>12.00372525</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2955007672457653</v>
+        <v>0.3001938025905673</v>
       </c>
       <c r="T55">
-        <v>3.633450414557267</v>
+        <v>3.701739797113788</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>13.87173005787551</v>
+        <v>13.61484616791485</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1584606491916609</v>
+        <v>0.1580416877778122</v>
       </c>
       <c r="C56">
-        <v>22.10055369760265</v>
+        <v>21.68425424182996</v>
       </c>
       <c r="D56">
-        <v>32.11055369760265</v>
+        <v>32.15925424182996</v>
       </c>
       <c r="E56">
-        <v>-6.59</v>
+        <v>-6.125</v>
       </c>
       <c r="F56">
-        <v>25.11</v>
+        <v>25.575</v>
       </c>
       <c r="G56">
         <v>15.1</v>
@@ -5873,28 +5873,28 @@
         <v>17.196</v>
       </c>
       <c r="M56">
-        <v>1.263033</v>
+        <v>1.2864225</v>
       </c>
       <c r="N56">
-        <v>15.932967</v>
+        <v>15.9095775</v>
       </c>
       <c r="O56">
-        <v>3.98324175</v>
+        <v>3.977394375</v>
       </c>
       <c r="P56">
-        <v>11.94972525</v>
+        <v>11.932183125</v>
       </c>
       <c r="Q56">
-        <v>12.00372525</v>
+        <v>11.986183125</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3001938025905673</v>
+        <v>0.3050954172840272</v>
       </c>
       <c r="T56">
-        <v>3.701739797113788</v>
+        <v>3.773064263339487</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>13.61484616791485</v>
+        <v>13.3673035103164</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1580416877778122</v>
+        <v>0.1576227263639635</v>
       </c>
       <c r="C57">
-        <v>21.68425424182996</v>
+        <v>21.26810273402502</v>
       </c>
       <c r="D57">
-        <v>32.15925424182996</v>
+        <v>32.20810273402502</v>
       </c>
       <c r="E57">
-        <v>-6.125</v>
+        <v>-5.66</v>
       </c>
       <c r="F57">
-        <v>25.575</v>
+        <v>26.04</v>
       </c>
       <c r="G57">
         <v>15.1</v>
@@ -5955,28 +5955,28 @@
         <v>17.196</v>
       </c>
       <c r="M57">
-        <v>1.2864225</v>
+        <v>1.309812</v>
       </c>
       <c r="N57">
-        <v>15.9095775</v>
+        <v>15.886188</v>
       </c>
       <c r="O57">
-        <v>3.977394375</v>
+        <v>3.971547</v>
       </c>
       <c r="P57">
-        <v>11.932183125</v>
+        <v>11.914641</v>
       </c>
       <c r="Q57">
-        <v>11.986183125</v>
+        <v>11.968641</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3050954172840272</v>
+        <v>0.3102198326453716</v>
       </c>
       <c r="T57">
-        <v>3.773064263339487</v>
+        <v>3.847630750757263</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>13.3673035103164</v>
+        <v>13.12860166191789</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1576227263639635</v>
+        <v>0.1572037649501147</v>
       </c>
       <c r="C58">
-        <v>21.26810273402502</v>
+        <v>20.85209984939279</v>
       </c>
       <c r="D58">
-        <v>32.20810273402502</v>
+        <v>32.25709984939279</v>
       </c>
       <c r="E58">
-        <v>-5.66</v>
+        <v>-5.195</v>
       </c>
       <c r="F58">
-        <v>26.04</v>
+        <v>26.505</v>
       </c>
       <c r="G58">
         <v>15.1</v>
@@ -6037,28 +6037,28 @@
         <v>17.196</v>
       </c>
       <c r="M58">
-        <v>1.309812</v>
+        <v>1.3332015</v>
       </c>
       <c r="N58">
-        <v>15.886188</v>
+        <v>15.8627985</v>
       </c>
       <c r="O58">
-        <v>3.971547</v>
+        <v>3.965699625000001</v>
       </c>
       <c r="P58">
-        <v>11.914641</v>
+        <v>11.897098875</v>
       </c>
       <c r="Q58">
-        <v>11.968641</v>
+        <v>11.951098875</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3102198326453716</v>
+        <v>0.3155825929072436</v>
       </c>
       <c r="T58">
-        <v>3.847630750757263</v>
+        <v>3.925665446892146</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>13.12860166191789</v>
+        <v>12.89827531697197</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1572037649501147</v>
+        <v>0.157437303536266</v>
       </c>
       <c r="C59">
-        <v>20.85209984939279</v>
+        <v>20.35976937390204</v>
       </c>
       <c r="D59">
-        <v>32.25709984939279</v>
+        <v>32.22976937390204</v>
       </c>
       <c r="E59">
-        <v>-5.195</v>
+        <v>-4.73</v>
       </c>
       <c r="F59">
-        <v>26.505</v>
+        <v>26.97</v>
       </c>
       <c r="G59">
         <v>15.1</v>
@@ -6119,45 +6119,45 @@
         <v>17.196</v>
       </c>
       <c r="M59">
-        <v>1.3332015</v>
+        <v>1.397046</v>
       </c>
       <c r="N59">
-        <v>15.8627985</v>
+        <v>15.798954</v>
       </c>
       <c r="O59">
-        <v>3.965699625000001</v>
+        <v>3.9497385</v>
       </c>
       <c r="P59">
-        <v>11.897098875</v>
+        <v>11.8492155</v>
       </c>
       <c r="Q59">
-        <v>11.951098875</v>
+        <v>11.9032155</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3155825929072436</v>
+        <v>0.3212007227053953</v>
       </c>
       <c r="T59">
-        <v>3.925665446892146</v>
+        <v>4.007416080938214</v>
       </c>
       <c r="U59">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y59">
-        <v>12.89827531697197</v>
+        <v>12.30882877156515</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.157437303536266</v>
+        <v>0.1570295921224173</v>
       </c>
       <c r="C60">
-        <v>20.35976937390205</v>
+        <v>19.94251308327818</v>
       </c>
       <c r="D60">
-        <v>32.22976937390204</v>
+        <v>32.27751308327818</v>
       </c>
       <c r="E60">
-        <v>-4.730000000000004</v>
+        <v>-4.265000000000004</v>
       </c>
       <c r="F60">
-        <v>26.97</v>
+        <v>27.435</v>
       </c>
       <c r="G60">
         <v>15.1</v>
@@ -6201,28 +6201,28 @@
         <v>17.196</v>
       </c>
       <c r="M60">
-        <v>1.397046</v>
+        <v>1.421133</v>
       </c>
       <c r="N60">
-        <v>15.798954</v>
+        <v>15.774867</v>
       </c>
       <c r="O60">
-        <v>3.9497385</v>
+        <v>3.943716750000001</v>
       </c>
       <c r="P60">
-        <v>11.8492155</v>
+        <v>11.83115025</v>
       </c>
       <c r="Q60">
-        <v>11.9032155</v>
+        <v>11.88515025</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3212007227053953</v>
+        <v>0.3270929076156519</v>
       </c>
       <c r="T60">
-        <v>4.007416080938213</v>
+        <v>4.093154550791405</v>
       </c>
       <c r="U60">
         <v>0.0518</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>12.30882877156515</v>
+        <v>12.10020455509794</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1570295921224173</v>
+        <v>0.1566218807085686</v>
       </c>
       <c r="C61">
-        <v>19.94251308327818</v>
+        <v>19.52539845320788</v>
       </c>
       <c r="D61">
-        <v>32.27751308327818</v>
+        <v>32.32539845320788</v>
       </c>
       <c r="E61">
-        <v>-4.265000000000004</v>
+        <v>-3.800000000000004</v>
       </c>
       <c r="F61">
-        <v>27.435</v>
+        <v>27.9</v>
       </c>
       <c r="G61">
         <v>15.1</v>
@@ -6283,28 +6283,28 @@
         <v>17.196</v>
       </c>
       <c r="M61">
-        <v>1.421133</v>
+        <v>1.44522</v>
       </c>
       <c r="N61">
-        <v>15.774867</v>
+        <v>15.75078</v>
       </c>
       <c r="O61">
-        <v>3.943716750000001</v>
+        <v>3.937695000000001</v>
       </c>
       <c r="P61">
-        <v>11.83115025</v>
+        <v>11.813085</v>
       </c>
       <c r="Q61">
-        <v>11.88515025</v>
+        <v>11.867085</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3270929076156519</v>
+        <v>0.3332797017714214</v>
       </c>
       <c r="T61">
-        <v>4.093154550791405</v>
+        <v>4.183179944137257</v>
       </c>
       <c r="U61">
         <v>0.0518</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>12.10020455509794</v>
+        <v>11.89853447917964</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1566218807085686</v>
+        <v>0.1562141692947199</v>
       </c>
       <c r="C62">
-        <v>19.52539845320788</v>
+        <v>19.10842611511027</v>
       </c>
       <c r="D62">
-        <v>32.32539845320788</v>
+        <v>32.37342611511027</v>
       </c>
       <c r="E62">
-        <v>-3.800000000000004</v>
+        <v>-3.335000000000004</v>
       </c>
       <c r="F62">
-        <v>27.9</v>
+        <v>28.365</v>
       </c>
       <c r="G62">
         <v>15.1</v>
@@ -6365,28 +6365,28 @@
         <v>17.196</v>
       </c>
       <c r="M62">
-        <v>1.44522</v>
+        <v>1.469307</v>
       </c>
       <c r="N62">
-        <v>15.75078</v>
+        <v>15.726693</v>
       </c>
       <c r="O62">
-        <v>3.937695000000001</v>
+        <v>3.93167325</v>
       </c>
       <c r="P62">
-        <v>11.813085</v>
+        <v>11.79501975</v>
       </c>
       <c r="Q62">
-        <v>11.867085</v>
+        <v>11.84901975</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3332797017714214</v>
+        <v>0.3397837674223586</v>
       </c>
       <c r="T62">
-        <v>4.183179944137257</v>
+        <v>4.277822024321359</v>
       </c>
       <c r="U62">
         <v>0.0518</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>11.89853447917964</v>
+        <v>11.70347653689801</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1562141692947199</v>
+        <v>0.1558064578808711</v>
       </c>
       <c r="C63">
-        <v>19.10842611511027</v>
+        <v>18.69159670416263</v>
       </c>
       <c r="D63">
-        <v>32.37342611511027</v>
+        <v>32.42159670416262</v>
       </c>
       <c r="E63">
-        <v>-3.335000000000004</v>
+        <v>-2.870000000000005</v>
       </c>
       <c r="F63">
-        <v>28.365</v>
+        <v>28.83</v>
       </c>
       <c r="G63">
         <v>15.1</v>
@@ -6447,28 +6447,28 @@
         <v>17.196</v>
       </c>
       <c r="M63">
-        <v>1.469307</v>
+        <v>1.493394</v>
       </c>
       <c r="N63">
-        <v>15.726693</v>
+        <v>15.702606</v>
       </c>
       <c r="O63">
-        <v>3.93167325</v>
+        <v>3.9256515</v>
       </c>
       <c r="P63">
-        <v>11.79501975</v>
+        <v>11.7769545</v>
       </c>
       <c r="Q63">
-        <v>11.84901975</v>
+        <v>11.8309545</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3397837674223586</v>
+        <v>0.3466301523180819</v>
       </c>
       <c r="T63">
-        <v>4.277822024321359</v>
+        <v>4.377445266620412</v>
       </c>
       <c r="U63">
         <v>0.0518</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>11.70347653689801</v>
+        <v>11.51471078630288</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1558064578808711</v>
+        <v>0.1553987464670223</v>
       </c>
       <c r="C64">
-        <v>18.69159670416263</v>
+        <v>18.27491085932835</v>
       </c>
       <c r="D64">
-        <v>32.42159670416262</v>
+        <v>32.46991085932835</v>
       </c>
       <c r="E64">
-        <v>-2.870000000000005</v>
+        <v>-2.405000000000001</v>
       </c>
       <c r="F64">
-        <v>28.83</v>
+        <v>29.295</v>
       </c>
       <c r="G64">
         <v>15.1</v>
@@ -6529,28 +6529,28 @@
         <v>17.196</v>
       </c>
       <c r="M64">
-        <v>1.493394</v>
+        <v>1.517481</v>
       </c>
       <c r="N64">
-        <v>15.702606</v>
+        <v>15.678519</v>
       </c>
       <c r="O64">
-        <v>3.9256515</v>
+        <v>3.91962975</v>
       </c>
       <c r="P64">
-        <v>11.7769545</v>
+        <v>11.75888925</v>
       </c>
       <c r="Q64">
-        <v>11.8309545</v>
+        <v>11.81288925</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3466301523180819</v>
+        <v>0.3538466120730334</v>
       </c>
       <c r="T64">
-        <v>4.377445266620412</v>
+        <v>4.482453549043738</v>
       </c>
       <c r="U64">
         <v>0.0518</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>11.51471078630288</v>
+        <v>11.3319375992187</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1553987464670223</v>
+        <v>0.1549910350531736</v>
       </c>
       <c r="C65">
-        <v>18.27491085932835</v>
+        <v>17.85836922338521</v>
       </c>
       <c r="D65">
-        <v>32.46991085932835</v>
+        <v>32.51836922338521</v>
       </c>
       <c r="E65">
-        <v>-2.405000000000001</v>
+        <v>-1.940000000000001</v>
       </c>
       <c r="F65">
-        <v>29.295</v>
+        <v>29.76</v>
       </c>
       <c r="G65">
         <v>15.1</v>
@@ -6611,28 +6611,28 @@
         <v>17.196</v>
       </c>
       <c r="M65">
-        <v>1.517481</v>
+        <v>1.541568</v>
       </c>
       <c r="N65">
-        <v>15.678519</v>
+        <v>15.654432</v>
       </c>
       <c r="O65">
-        <v>3.91962975</v>
+        <v>3.913608</v>
       </c>
       <c r="P65">
-        <v>11.75888925</v>
+        <v>11.740824</v>
       </c>
       <c r="Q65">
-        <v>11.81288925</v>
+        <v>11.794824</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3538466120730334</v>
+        <v>0.3614639862588157</v>
       </c>
       <c r="T65">
-        <v>4.482453549043738</v>
+        <v>4.593295624935028</v>
       </c>
       <c r="U65">
         <v>0.0518</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>11.3319375992187</v>
+        <v>11.15487607423091</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1549910350531736</v>
+        <v>0.1545833236393249</v>
       </c>
       <c r="C66">
-        <v>17.85836922338521</v>
+        <v>17.44197244295385</v>
       </c>
       <c r="D66">
-        <v>32.51836922338521</v>
+        <v>32.56697244295385</v>
       </c>
       <c r="E66">
-        <v>-1.940000000000001</v>
+        <v>-1.475000000000001</v>
       </c>
       <c r="F66">
-        <v>29.76</v>
+        <v>30.225</v>
       </c>
       <c r="G66">
         <v>15.1</v>
@@ -6693,28 +6693,28 @@
         <v>17.196</v>
       </c>
       <c r="M66">
-        <v>1.541568</v>
+        <v>1.565655</v>
       </c>
       <c r="N66">
-        <v>15.654432</v>
+        <v>15.630345</v>
       </c>
       <c r="O66">
-        <v>3.913608</v>
+        <v>3.90758625</v>
       </c>
       <c r="P66">
-        <v>11.740824</v>
+        <v>11.72275875</v>
       </c>
       <c r="Q66">
-        <v>11.794824</v>
+        <v>11.77675875</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3614639862588157</v>
+        <v>0.3695166389694998</v>
       </c>
       <c r="T66">
-        <v>4.593295624935028</v>
+        <v>4.710471533734391</v>
       </c>
       <c r="U66">
         <v>0.0518</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>11.15487607423091</v>
+        <v>10.98326259616582</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1545833236393249</v>
+        <v>0.1541756122254762</v>
       </c>
       <c r="C67">
-        <v>17.44197244295385</v>
+        <v>17.02572116852658</v>
       </c>
       <c r="D67">
-        <v>32.56697244295385</v>
+        <v>32.61572116852658</v>
       </c>
       <c r="E67">
-        <v>-1.475000000000001</v>
+        <v>-1.010000000000002</v>
       </c>
       <c r="F67">
-        <v>30.225</v>
+        <v>30.69</v>
       </c>
       <c r="G67">
         <v>15.1</v>
@@ -6775,28 +6775,28 @@
         <v>17.196</v>
       </c>
       <c r="M67">
-        <v>1.565655</v>
+        <v>1.589742</v>
       </c>
       <c r="N67">
-        <v>15.630345</v>
+        <v>15.606258</v>
       </c>
       <c r="O67">
-        <v>3.90758625</v>
+        <v>3.901564500000001</v>
       </c>
       <c r="P67">
-        <v>11.72275875</v>
+        <v>11.7046935</v>
       </c>
       <c r="Q67">
-        <v>11.77675875</v>
+        <v>11.7586935</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3695166389694998</v>
+        <v>0.3780429771337535</v>
       </c>
       <c r="T67">
-        <v>4.710471533734391</v>
+        <v>4.834540143051363</v>
       </c>
       <c r="U67">
         <v>0.0518</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>10.98326259616582</v>
+        <v>10.81684952652695</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1541756122254762</v>
+        <v>0.1537679008116274</v>
       </c>
       <c r="C68">
-        <v>17.02572116852658</v>
+        <v>16.60961605449636</v>
       </c>
       <c r="D68">
-        <v>32.61572116852658</v>
+        <v>32.66461605449636</v>
       </c>
       <c r="E68">
-        <v>-1.010000000000002</v>
+        <v>-0.5450000000000017</v>
       </c>
       <c r="F68">
-        <v>30.69</v>
+        <v>31.155</v>
       </c>
       <c r="G68">
         <v>15.1</v>
@@ -6857,28 +6857,28 @@
         <v>17.196</v>
       </c>
       <c r="M68">
-        <v>1.589742</v>
+        <v>1.613829</v>
       </c>
       <c r="N68">
-        <v>15.606258</v>
+        <v>15.582171</v>
       </c>
       <c r="O68">
-        <v>3.901564500000001</v>
+        <v>3.895542750000001</v>
       </c>
       <c r="P68">
-        <v>11.7046935</v>
+        <v>11.68662825</v>
       </c>
       <c r="Q68">
-        <v>11.7586935</v>
+        <v>11.74062825</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3780429771337535</v>
+        <v>0.3870860630655377</v>
       </c>
       <c r="T68">
-        <v>4.834540143051363</v>
+        <v>4.96612806202391</v>
       </c>
       <c r="U68">
         <v>0.0518</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>10.81684952652695</v>
+        <v>10.65540401120565</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1537679008116274</v>
+        <v>0.1533601893977787</v>
       </c>
       <c r="C69">
-        <v>16.60961605449636</v>
+        <v>16.19365775918611</v>
       </c>
       <c r="D69">
-        <v>32.66461605449636</v>
+        <v>32.71365775918611</v>
       </c>
       <c r="E69">
-        <v>-0.5450000000000017</v>
+        <v>-0.08000000000000185</v>
       </c>
       <c r="F69">
-        <v>31.155</v>
+        <v>31.62</v>
       </c>
       <c r="G69">
         <v>15.1</v>
@@ -6939,28 +6939,28 @@
         <v>17.196</v>
       </c>
       <c r="M69">
-        <v>1.613829</v>
+        <v>1.637916</v>
       </c>
       <c r="N69">
-        <v>15.582171</v>
+        <v>15.558084</v>
       </c>
       <c r="O69">
-        <v>3.895542750000001</v>
+        <v>3.889521</v>
       </c>
       <c r="P69">
-        <v>11.68662825</v>
+        <v>11.668563</v>
       </c>
       <c r="Q69">
-        <v>11.74062825</v>
+        <v>11.722563</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3870860630655377</v>
+        <v>0.3966943418680585</v>
       </c>
       <c r="T69">
-        <v>4.96612806202391</v>
+        <v>5.105940225932241</v>
       </c>
       <c r="U69">
         <v>0.0518</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>10.65540401120565</v>
+        <v>10.4987068933938</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1533601893977787</v>
+        <v>0.15295247798393</v>
       </c>
       <c r="C70">
-        <v>16.19365775918611</v>
+        <v>15.7778469448782</v>
       </c>
       <c r="D70">
-        <v>32.71365775918611</v>
+        <v>32.7628469448782</v>
       </c>
       <c r="E70">
-        <v>-0.08000000000000185</v>
+        <v>0.384999999999998</v>
       </c>
       <c r="F70">
-        <v>31.62</v>
+        <v>32.085</v>
       </c>
       <c r="G70">
         <v>15.1</v>
@@ -7021,28 +7021,28 @@
         <v>17.196</v>
       </c>
       <c r="M70">
-        <v>1.637916</v>
+        <v>1.662003</v>
       </c>
       <c r="N70">
-        <v>15.558084</v>
+        <v>15.533997</v>
       </c>
       <c r="O70">
-        <v>3.889521</v>
+        <v>3.88349925</v>
       </c>
       <c r="P70">
-        <v>11.668563</v>
+        <v>11.65049775</v>
       </c>
       <c r="Q70">
-        <v>11.722563</v>
+        <v>11.70449775</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3966943418680585</v>
+        <v>0.4069225096255806</v>
       </c>
       <c r="T70">
-        <v>5.105940225932241</v>
+        <v>5.254772529447561</v>
       </c>
       <c r="U70">
         <v>0.0518</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>10.4987068933938</v>
+        <v>10.34655172102578</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.15295247798393</v>
+        <v>0.1525447665700812</v>
       </c>
       <c r="C71">
-        <v>15.7778469448782</v>
+        <v>15.36218427784438</v>
       </c>
       <c r="D71">
-        <v>32.7628469448782</v>
+        <v>32.81218427784438</v>
       </c>
       <c r="E71">
-        <v>0.384999999999998</v>
+        <v>0.8500000000000014</v>
       </c>
       <c r="F71">
-        <v>32.085</v>
+        <v>32.55</v>
       </c>
       <c r="G71">
         <v>15.1</v>
@@ -7103,28 +7103,28 @@
         <v>17.196</v>
       </c>
       <c r="M71">
-        <v>1.662003</v>
+        <v>1.68609</v>
       </c>
       <c r="N71">
-        <v>15.533997</v>
+        <v>15.50991</v>
       </c>
       <c r="O71">
-        <v>3.88349925</v>
+        <v>3.8774775</v>
       </c>
       <c r="P71">
-        <v>11.65049775</v>
+        <v>11.6324325</v>
       </c>
       <c r="Q71">
-        <v>11.70449775</v>
+        <v>11.6864325</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4069225096255806</v>
+        <v>0.4178325552336042</v>
       </c>
       <c r="T71">
-        <v>5.254772529447561</v>
+        <v>5.413526986530569</v>
       </c>
       <c r="U71">
         <v>0.0518</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>10.34655172102578</v>
+        <v>10.19874383929684</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1525447665700812</v>
+        <v>0.1521370551562325</v>
       </c>
       <c r="C72">
-        <v>15.36218427784438</v>
+        <v>14.94667042837572</v>
       </c>
       <c r="D72">
-        <v>32.81218427784438</v>
+        <v>32.86167042837572</v>
       </c>
       <c r="E72">
-        <v>0.8500000000000014</v>
+        <v>1.314999999999998</v>
       </c>
       <c r="F72">
-        <v>32.55</v>
+        <v>33.015</v>
       </c>
       <c r="G72">
         <v>15.1</v>
@@ -7185,28 +7185,28 @@
         <v>17.196</v>
       </c>
       <c r="M72">
-        <v>1.68609</v>
+        <v>1.710177</v>
       </c>
       <c r="N72">
-        <v>15.50991</v>
+        <v>15.485823</v>
       </c>
       <c r="O72">
-        <v>3.8774775</v>
+        <v>3.87145575</v>
       </c>
       <c r="P72">
-        <v>11.6324325</v>
+        <v>11.61436725</v>
       </c>
       <c r="Q72">
-        <v>11.6864325</v>
+        <v>11.66836725</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4178325552336042</v>
+        <v>0.4294950177801123</v>
       </c>
       <c r="T72">
-        <v>5.413526986530569</v>
+        <v>5.583230026860682</v>
       </c>
       <c r="U72">
         <v>0.0518</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>10.19874383929684</v>
+        <v>10.05509955987012</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1521370551562325</v>
+        <v>0.1517293437423838</v>
       </c>
       <c r="C73">
-        <v>14.94667042837572</v>
+        <v>14.53130607081307</v>
       </c>
       <c r="D73">
-        <v>32.86167042837572</v>
+        <v>32.91130607081306</v>
       </c>
       <c r="E73">
-        <v>1.314999999999998</v>
+        <v>1.779999999999994</v>
       </c>
       <c r="F73">
-        <v>33.015</v>
+        <v>33.48</v>
       </c>
       <c r="G73">
         <v>15.1</v>
@@ -7267,28 +7267,28 @@
         <v>17.196</v>
       </c>
       <c r="M73">
-        <v>1.710177</v>
+        <v>1.734264</v>
       </c>
       <c r="N73">
-        <v>15.485823</v>
+        <v>15.461736</v>
       </c>
       <c r="O73">
-        <v>3.87145575</v>
+        <v>3.865434</v>
       </c>
       <c r="P73">
-        <v>11.61436725</v>
+        <v>11.596302</v>
       </c>
       <c r="Q73">
-        <v>11.66836725</v>
+        <v>11.650302</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4294950177801121</v>
+        <v>0.4419905133656564</v>
       </c>
       <c r="T73">
-        <v>5.58323002686068</v>
+        <v>5.765054712928657</v>
       </c>
       <c r="U73">
         <v>0.0518</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>10.05509955987012</v>
+        <v>9.915445399316368</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1517293437423838</v>
+        <v>0.1522523823285351</v>
       </c>
       <c r="C74">
-        <v>14.53130607081307</v>
+        <v>14.00265740951656</v>
       </c>
       <c r="D74">
-        <v>32.91130607081306</v>
+        <v>32.84765740951656</v>
       </c>
       <c r="E74">
-        <v>1.779999999999994</v>
+        <v>2.244999999999997</v>
       </c>
       <c r="F74">
-        <v>33.48</v>
+        <v>33.945</v>
       </c>
       <c r="G74">
         <v>15.1</v>
@@ -7349,45 +7349,45 @@
         <v>17.196</v>
       </c>
       <c r="M74">
-        <v>1.734264</v>
+        <v>1.8160575</v>
       </c>
       <c r="N74">
-        <v>15.461736</v>
+        <v>15.3799425</v>
       </c>
       <c r="O74">
-        <v>3.865434</v>
+        <v>3.844985625000001</v>
       </c>
       <c r="P74">
-        <v>11.596302</v>
+        <v>11.534956875</v>
       </c>
       <c r="Q74">
-        <v>11.650302</v>
+        <v>11.588956875</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4419905133656564</v>
+        <v>0.4554116012167965</v>
       </c>
       <c r="T74">
-        <v>5.765054712928657</v>
+        <v>5.960347894260928</v>
       </c>
       <c r="U74">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>9.915445399316368</v>
+        <v>9.468863183021464</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1522523823285351</v>
+        <v>0.1518574209146863</v>
       </c>
       <c r="C75">
-        <v>14.00265740951656</v>
+        <v>13.58569754192725</v>
       </c>
       <c r="D75">
-        <v>32.84765740951656</v>
+        <v>32.89569754192724</v>
       </c>
       <c r="E75">
-        <v>2.244999999999997</v>
+        <v>2.709999999999994</v>
       </c>
       <c r="F75">
-        <v>33.945</v>
+        <v>34.41</v>
       </c>
       <c r="G75">
         <v>15.1</v>
@@ -7431,28 +7431,28 @@
         <v>17.196</v>
       </c>
       <c r="M75">
-        <v>1.8160575</v>
+        <v>1.840935</v>
       </c>
       <c r="N75">
-        <v>15.3799425</v>
+        <v>15.355065</v>
       </c>
       <c r="O75">
-        <v>3.844985625000001</v>
+        <v>3.83876625</v>
       </c>
       <c r="P75">
-        <v>11.534956875</v>
+        <v>11.51629875</v>
       </c>
       <c r="Q75">
-        <v>11.588956875</v>
+        <v>11.57029875</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4554116012167965</v>
+        <v>0.4698650804411012</v>
       </c>
       <c r="T75">
-        <v>5.960347894260928</v>
+        <v>6.170663628003374</v>
       </c>
       <c r="U75">
         <v>0.0535</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>9.468863183021464</v>
+        <v>9.340905572440093</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1518574209146863</v>
+        <v>0.1514624595008376</v>
       </c>
       <c r="C76">
-        <v>13.58569754192725</v>
+        <v>13.16887839880447</v>
       </c>
       <c r="D76">
-        <v>32.89569754192724</v>
+        <v>32.94387839880447</v>
       </c>
       <c r="E76">
-        <v>2.709999999999994</v>
+        <v>3.174999999999997</v>
       </c>
       <c r="F76">
-        <v>34.41</v>
+        <v>34.875</v>
       </c>
       <c r="G76">
         <v>15.1</v>
@@ -7513,28 +7513,28 @@
         <v>17.196</v>
       </c>
       <c r="M76">
-        <v>1.840935</v>
+        <v>1.8658125</v>
       </c>
       <c r="N76">
-        <v>15.355065</v>
+        <v>15.3301875</v>
       </c>
       <c r="O76">
-        <v>3.83876625</v>
+        <v>3.832546875</v>
       </c>
       <c r="P76">
-        <v>11.51629875</v>
+        <v>11.497640625</v>
       </c>
       <c r="Q76">
-        <v>11.57029875</v>
+        <v>11.551640625</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4698650804411012</v>
+        <v>0.4854748380033503</v>
       </c>
       <c r="T76">
-        <v>6.170663628003374</v>
+        <v>6.397804620445217</v>
       </c>
       <c r="U76">
         <v>0.0535</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>9.340905572440093</v>
+        <v>9.216360164807558</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1514624595008376</v>
+        <v>0.1510674980869888</v>
       </c>
       <c r="C77">
-        <v>13.16887839880447</v>
+        <v>12.75220059939372</v>
       </c>
       <c r="D77">
-        <v>32.94387839880447</v>
+        <v>32.99220059939372</v>
       </c>
       <c r="E77">
-        <v>3.174999999999997</v>
+        <v>3.640000000000001</v>
       </c>
       <c r="F77">
-        <v>34.875</v>
+        <v>35.34</v>
       </c>
       <c r="G77">
         <v>15.1</v>
@@ -7595,28 +7595,28 @@
         <v>17.196</v>
       </c>
       <c r="M77">
-        <v>1.8658125</v>
+        <v>1.89069</v>
       </c>
       <c r="N77">
-        <v>15.3301875</v>
+        <v>15.30531</v>
       </c>
       <c r="O77">
-        <v>3.832546875</v>
+        <v>3.826327500000001</v>
       </c>
       <c r="P77">
-        <v>11.497640625</v>
+        <v>11.4789825</v>
       </c>
       <c r="Q77">
-        <v>11.551640625</v>
+        <v>11.5329825</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4854748380033503</v>
+        <v>0.5023854086957869</v>
       </c>
       <c r="T77">
-        <v>6.397804620445217</v>
+        <v>6.643874028923879</v>
       </c>
       <c r="U77">
         <v>0.0535</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>9.216360164807558</v>
+        <v>9.095092267902194</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1510674980869888</v>
+        <v>0.1506725366731401</v>
       </c>
       <c r="C78">
-        <v>12.75220059939372</v>
+        <v>12.33566476657904</v>
       </c>
       <c r="D78">
-        <v>32.99220059939372</v>
+        <v>33.04066476657904</v>
       </c>
       <c r="E78">
-        <v>3.640000000000001</v>
+        <v>4.104999999999997</v>
       </c>
       <c r="F78">
-        <v>35.34</v>
+        <v>35.805</v>
       </c>
       <c r="G78">
         <v>15.1</v>
@@ -7677,28 +7677,28 @@
         <v>17.196</v>
       </c>
       <c r="M78">
-        <v>1.89069</v>
+        <v>1.9155675</v>
       </c>
       <c r="N78">
-        <v>15.30531</v>
+        <v>15.2804325</v>
       </c>
       <c r="O78">
-        <v>3.826327500000001</v>
+        <v>3.820108125</v>
       </c>
       <c r="P78">
-        <v>11.4789825</v>
+        <v>11.460324375</v>
       </c>
       <c r="Q78">
-        <v>11.5329825</v>
+        <v>11.514324375</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5023854086957869</v>
+        <v>0.5207664637962615</v>
       </c>
       <c r="T78">
-        <v>6.643874028923879</v>
+        <v>6.911340777270252</v>
       </c>
       <c r="U78">
         <v>0.0535</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>9.095092267902194</v>
+        <v>8.976974186500868</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1506725366731401</v>
+        <v>0.1502775752592914</v>
       </c>
       <c r="C79">
-        <v>12.33566476657904</v>
+        <v>11.91927152690985</v>
       </c>
       <c r="D79">
-        <v>33.04066476657904</v>
+        <v>33.08927152690985</v>
       </c>
       <c r="E79">
-        <v>4.104999999999997</v>
+        <v>4.57</v>
       </c>
       <c r="F79">
-        <v>35.805</v>
+        <v>36.27</v>
       </c>
       <c r="G79">
         <v>15.1</v>
@@ -7759,28 +7759,28 @@
         <v>17.196</v>
       </c>
       <c r="M79">
-        <v>1.9155675</v>
+        <v>1.940445</v>
       </c>
       <c r="N79">
-        <v>15.2804325</v>
+        <v>15.255555</v>
       </c>
       <c r="O79">
-        <v>3.820108125</v>
+        <v>3.81388875</v>
       </c>
       <c r="P79">
-        <v>11.460324375</v>
+        <v>11.44166625</v>
       </c>
       <c r="Q79">
-        <v>11.514324375</v>
+        <v>11.49566625</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5207664637962615</v>
+        <v>0.54081852390587</v>
       </c>
       <c r="T79">
-        <v>6.911340777270252</v>
+        <v>7.203122684557203</v>
       </c>
       <c r="U79">
         <v>0.0535</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>8.976974186500868</v>
+        <v>8.86188477385342</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1502775752592914</v>
+        <v>0.1498826138454427</v>
       </c>
       <c r="C80">
-        <v>11.91927152690985</v>
+        <v>11.5030215106279</v>
       </c>
       <c r="D80">
-        <v>33.08927152690985</v>
+        <v>33.1380215106279</v>
       </c>
       <c r="E80">
-        <v>4.57</v>
+        <v>5.034999999999997</v>
       </c>
       <c r="F80">
-        <v>36.27</v>
+        <v>36.735</v>
       </c>
       <c r="G80">
         <v>15.1</v>
@@ -7841,28 +7841,28 @@
         <v>17.196</v>
       </c>
       <c r="M80">
-        <v>1.940445</v>
+        <v>1.9653225</v>
       </c>
       <c r="N80">
-        <v>15.255555</v>
+        <v>15.2306775</v>
       </c>
       <c r="O80">
-        <v>3.81388875</v>
+        <v>3.807669375000001</v>
       </c>
       <c r="P80">
-        <v>11.44166625</v>
+        <v>11.423008125</v>
       </c>
       <c r="Q80">
-        <v>11.49566625</v>
+        <v>11.477008125</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.54081852390587</v>
+        <v>0.5627803040259175</v>
       </c>
       <c r="T80">
-        <v>7.203122684557203</v>
+        <v>7.522693344919102</v>
       </c>
       <c r="U80">
         <v>0.0535</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>8.86188477385342</v>
+        <v>8.749709017222365</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1498826138454427</v>
+        <v>0.1494876524315939</v>
       </c>
       <c r="C81">
-        <v>11.5030215106279</v>
+        <v>11.08691535169454</v>
       </c>
       <c r="D81">
-        <v>33.1380215106279</v>
+        <v>33.18691535169454</v>
       </c>
       <c r="E81">
-        <v>5.034999999999997</v>
+        <v>5.5</v>
       </c>
       <c r="F81">
-        <v>36.735</v>
+        <v>37.2</v>
       </c>
       <c r="G81">
         <v>15.1</v>
@@ -7923,28 +7923,28 @@
         <v>17.196</v>
       </c>
       <c r="M81">
-        <v>1.9653225</v>
+        <v>1.9902</v>
       </c>
       <c r="N81">
-        <v>15.2306775</v>
+        <v>15.2058</v>
       </c>
       <c r="O81">
-        <v>3.807669375000001</v>
+        <v>3.80145</v>
       </c>
       <c r="P81">
-        <v>11.423008125</v>
+        <v>11.40435</v>
       </c>
       <c r="Q81">
-        <v>11.477008125</v>
+        <v>11.45835</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5627803040259175</v>
+        <v>0.5869382621579697</v>
       </c>
       <c r="T81">
-        <v>7.522693344919102</v>
+        <v>7.874221071317192</v>
       </c>
       <c r="U81">
         <v>0.0535</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>8.749709017222365</v>
+        <v>8.640337654507086</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1494876524315939</v>
+        <v>0.1490926910177452</v>
       </c>
       <c r="C82">
-        <v>11.08691535169454</v>
+        <v>10.67095368781816</v>
       </c>
       <c r="D82">
-        <v>33.18691535169454</v>
+        <v>33.23595368781816</v>
       </c>
       <c r="E82">
-        <v>5.5</v>
+        <v>5.964999999999996</v>
       </c>
       <c r="F82">
-        <v>37.2</v>
+        <v>37.665</v>
       </c>
       <c r="G82">
         <v>15.1</v>
@@ -8005,28 +8005,28 @@
         <v>17.196</v>
       </c>
       <c r="M82">
-        <v>1.9902</v>
+        <v>2.0150775</v>
       </c>
       <c r="N82">
-        <v>15.2058</v>
+        <v>15.1809225</v>
       </c>
       <c r="O82">
-        <v>3.80145</v>
+        <v>3.795230625</v>
       </c>
       <c r="P82">
-        <v>11.40435</v>
+        <v>11.385691875</v>
       </c>
       <c r="Q82">
-        <v>11.45835</v>
+        <v>11.439691875</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5869382621579697</v>
+        <v>0.6136391632512906</v>
       </c>
       <c r="T82">
-        <v>7.874221071317192</v>
+        <v>8.262751716283502</v>
       </c>
       <c r="U82">
         <v>0.0535</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>8.640337654507086</v>
+        <v>8.533666819266259</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1490926910177452</v>
+        <v>0.1486977296038965</v>
       </c>
       <c r="C83">
-        <v>10.67095368781816</v>
+        <v>10.25513716048199</v>
       </c>
       <c r="D83">
-        <v>33.23595368781816</v>
+        <v>33.28513716048199</v>
       </c>
       <c r="E83">
-        <v>5.964999999999996</v>
+        <v>6.43</v>
       </c>
       <c r="F83">
-        <v>37.665</v>
+        <v>38.13</v>
       </c>
       <c r="G83">
         <v>15.1</v>
@@ -8087,28 +8087,28 @@
         <v>17.196</v>
       </c>
       <c r="M83">
-        <v>2.0150775</v>
+        <v>2.039955</v>
       </c>
       <c r="N83">
-        <v>15.1809225</v>
+        <v>15.156045</v>
       </c>
       <c r="O83">
-        <v>3.795230625</v>
+        <v>3.789011250000001</v>
       </c>
       <c r="P83">
-        <v>11.385691875</v>
+        <v>11.36703375</v>
       </c>
       <c r="Q83">
-        <v>11.439691875</v>
+        <v>11.42103375</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6136391632512906</v>
+        <v>0.6433068311327583</v>
       </c>
       <c r="T83">
-        <v>8.262751716283502</v>
+        <v>8.694452432912733</v>
       </c>
       <c r="U83">
         <v>0.0535</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>8.533666819266259</v>
+        <v>8.42959771171423</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1486977296038965</v>
+        <v>0.1483027681900477</v>
       </c>
       <c r="C84">
-        <v>10.25513716048199</v>
+        <v>9.83946641497198</v>
       </c>
       <c r="D84">
-        <v>33.28513716048199</v>
+        <v>33.33446641497198</v>
       </c>
       <c r="E84">
-        <v>6.43</v>
+        <v>6.895000000000003</v>
       </c>
       <c r="F84">
-        <v>38.13</v>
+        <v>38.59500000000001</v>
       </c>
       <c r="G84">
         <v>15.1</v>
@@ -8169,28 +8169,28 @@
         <v>17.196</v>
       </c>
       <c r="M84">
-        <v>2.039955</v>
+        <v>2.0648325</v>
       </c>
       <c r="N84">
-        <v>15.156045</v>
+        <v>15.1311675</v>
       </c>
       <c r="O84">
-        <v>3.789011250000001</v>
+        <v>3.782791875</v>
       </c>
       <c r="P84">
-        <v>11.36703375</v>
+        <v>11.348375625</v>
       </c>
       <c r="Q84">
-        <v>11.42103375</v>
+        <v>11.402375625</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6433068311327583</v>
+        <v>0.676464812882634</v>
       </c>
       <c r="T84">
-        <v>8.694452432912733</v>
+        <v>9.176941469145406</v>
       </c>
       <c r="U84">
         <v>0.0535</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>8.42959771171423</v>
+        <v>8.328036293500805</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1483027681900477</v>
+        <v>0.147907806776199</v>
       </c>
       <c r="C85">
-        <v>9.83946641497198</v>
+        <v>9.423942100405093</v>
       </c>
       <c r="D85">
-        <v>33.33446641497198</v>
+        <v>33.38394210040509</v>
       </c>
       <c r="E85">
-        <v>6.895000000000003</v>
+        <v>7.359999999999999</v>
       </c>
       <c r="F85">
-        <v>38.59500000000001</v>
+        <v>39.06</v>
       </c>
       <c r="G85">
         <v>15.1</v>
@@ -8251,28 +8251,28 @@
         <v>17.196</v>
       </c>
       <c r="M85">
-        <v>2.0648325</v>
+        <v>2.08971</v>
       </c>
       <c r="N85">
-        <v>15.1311675</v>
+        <v>15.10629</v>
       </c>
       <c r="O85">
-        <v>3.782791875</v>
+        <v>3.7765725</v>
       </c>
       <c r="P85">
-        <v>11.348375625</v>
+        <v>11.3297175</v>
       </c>
       <c r="Q85">
-        <v>11.402375625</v>
+        <v>11.3837175</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.676464812882634</v>
+        <v>0.7137675423512441</v>
       </c>
       <c r="T85">
-        <v>9.176941469145406</v>
+        <v>9.719741634907161</v>
       </c>
       <c r="U85">
         <v>0.0535</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>8.328036293500805</v>
+        <v>8.228893004292463</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.147907806776199</v>
+        <v>0.1475128453623503</v>
       </c>
       <c r="C86">
-        <v>9.4239421004051</v>
+        <v>9.008564869757748</v>
       </c>
       <c r="D86">
-        <v>33.38394210040509</v>
+        <v>33.43356486975775</v>
       </c>
       <c r="E86">
-        <v>7.359999999999992</v>
+        <v>7.824999999999996</v>
       </c>
       <c r="F86">
-        <v>39.06</v>
+        <v>39.525</v>
       </c>
       <c r="G86">
         <v>15.1</v>
@@ -8333,28 +8333,28 @@
         <v>17.196</v>
       </c>
       <c r="M86">
-        <v>2.08971</v>
+        <v>2.1145875</v>
       </c>
       <c r="N86">
-        <v>15.10629</v>
+        <v>15.0814125</v>
       </c>
       <c r="O86">
-        <v>3.7765725</v>
+        <v>3.770353125000001</v>
       </c>
       <c r="P86">
-        <v>11.3297175</v>
+        <v>11.311059375</v>
       </c>
       <c r="Q86">
-        <v>11.3837175</v>
+        <v>11.365059375</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7137675423512437</v>
+        <v>0.7560439690823351</v>
       </c>
       <c r="T86">
-        <v>9.719741634907155</v>
+        <v>10.33491515610381</v>
       </c>
       <c r="U86">
         <v>0.0535</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>8.228893004292463</v>
+        <v>8.132082498359612</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1475128453623503</v>
+        <v>0.1471178839485015</v>
       </c>
       <c r="C87">
-        <v>9.008564869757748</v>
+        <v>8.593335379894526</v>
       </c>
       <c r="D87">
-        <v>33.43356486975775</v>
+        <v>33.48333537989453</v>
       </c>
       <c r="E87">
-        <v>7.824999999999996</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="F87">
-        <v>39.525</v>
+        <v>39.99</v>
       </c>
       <c r="G87">
         <v>15.1</v>
@@ -8415,28 +8415,28 @@
         <v>17.196</v>
       </c>
       <c r="M87">
-        <v>2.1145875</v>
+        <v>2.139465</v>
       </c>
       <c r="N87">
-        <v>15.0814125</v>
+        <v>15.056535</v>
       </c>
       <c r="O87">
-        <v>3.770353125000001</v>
+        <v>3.764133750000001</v>
       </c>
       <c r="P87">
-        <v>11.311059375</v>
+        <v>11.29240125</v>
       </c>
       <c r="Q87">
-        <v>11.365059375</v>
+        <v>11.34640125</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7560439690823351</v>
+        <v>0.8043598853464394</v>
       </c>
       <c r="T87">
-        <v>10.33491515610381</v>
+        <v>11.03797060889999</v>
       </c>
       <c r="U87">
         <v>0.0535</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>8.132082498359612</v>
+        <v>8.037523399541476</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1471178839485015</v>
+        <v>0.1467229225346528</v>
       </c>
       <c r="C88">
-        <v>8.593335379894526</v>
+        <v>8.178254291597206</v>
       </c>
       <c r="D88">
-        <v>33.48333537989453</v>
+        <v>33.5332542915972</v>
       </c>
       <c r="E88">
-        <v>8.289999999999999</v>
+        <v>8.754999999999995</v>
       </c>
       <c r="F88">
-        <v>39.99</v>
+        <v>40.455</v>
       </c>
       <c r="G88">
         <v>15.1</v>
@@ -8497,28 +8497,28 @@
         <v>17.196</v>
       </c>
       <c r="M88">
-        <v>2.139465</v>
+        <v>2.1643425</v>
       </c>
       <c r="N88">
-        <v>15.056535</v>
+        <v>15.0316575</v>
       </c>
       <c r="O88">
-        <v>3.764133750000001</v>
+        <v>3.757914375</v>
       </c>
       <c r="P88">
-        <v>11.29240125</v>
+        <v>11.273743125</v>
       </c>
       <c r="Q88">
-        <v>11.34640125</v>
+        <v>11.327743125</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8043598853464394</v>
+        <v>0.8601090194973291</v>
       </c>
       <c r="T88">
-        <v>11.03797060889999</v>
+        <v>11.84918843904942</v>
       </c>
       <c r="U88">
         <v>0.0535</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>8.037523399541476</v>
+        <v>7.945138073109963</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1467229225346528</v>
+        <v>0.1463279611208041</v>
       </c>
       <c r="C89">
-        <v>8.178254291597206</v>
+        <v>7.763322269593957</v>
       </c>
       <c r="D89">
-        <v>33.5332542915972</v>
+        <v>33.58332226959396</v>
       </c>
       <c r="E89">
-        <v>8.754999999999995</v>
+        <v>9.219999999999999</v>
       </c>
       <c r="F89">
-        <v>40.455</v>
+        <v>40.92</v>
       </c>
       <c r="G89">
         <v>15.1</v>
@@ -8579,28 +8579,28 @@
         <v>17.196</v>
       </c>
       <c r="M89">
-        <v>2.1643425</v>
+        <v>2.18922</v>
       </c>
       <c r="N89">
-        <v>15.0316575</v>
+        <v>15.00678</v>
       </c>
       <c r="O89">
-        <v>3.757914375</v>
+        <v>3.751695</v>
       </c>
       <c r="P89">
-        <v>11.273743125</v>
+        <v>11.255085</v>
       </c>
       <c r="Q89">
-        <v>11.327743125</v>
+        <v>11.309085</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8601090194973291</v>
+        <v>0.9251496760067006</v>
       </c>
       <c r="T89">
-        <v>11.84918843904942</v>
+        <v>12.79560924089043</v>
       </c>
       <c r="U89">
         <v>0.0535</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>7.945138073109963</v>
+        <v>7.854852413188259</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1463279611208041</v>
+        <v>0.1459329997069553</v>
       </c>
       <c r="C90">
-        <v>7.763322269593957</v>
+        <v>7.348539982588882</v>
       </c>
       <c r="D90">
-        <v>33.58332226959396</v>
+        <v>33.63353998258888</v>
       </c>
       <c r="E90">
-        <v>9.219999999999999</v>
+        <v>9.684999999999995</v>
       </c>
       <c r="F90">
-        <v>40.92</v>
+        <v>41.385</v>
       </c>
       <c r="G90">
         <v>15.1</v>
@@ -8661,28 +8661,28 @@
         <v>17.196</v>
       </c>
       <c r="M90">
-        <v>2.18922</v>
+        <v>2.2140975</v>
       </c>
       <c r="N90">
-        <v>15.00678</v>
+        <v>14.9819025</v>
       </c>
       <c r="O90">
-        <v>3.751695</v>
+        <v>3.745475625000001</v>
       </c>
       <c r="P90">
-        <v>11.255085</v>
+        <v>11.236426875</v>
       </c>
       <c r="Q90">
-        <v>11.309085</v>
+        <v>11.290426875</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9251496760067006</v>
+        <v>1.002015906426867</v>
       </c>
       <c r="T90">
-        <v>12.79560924089043</v>
+        <v>13.91410655215708</v>
       </c>
       <c r="U90">
         <v>0.0535</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>7.854852413188259</v>
+        <v>7.766595644500752</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1459329997069553</v>
+        <v>0.1455380382931066</v>
       </c>
       <c r="C91">
-        <v>7.348539982588882</v>
+        <v>6.933908103291749</v>
       </c>
       <c r="D91">
-        <v>33.63353998258888</v>
+        <v>33.68390810329175</v>
       </c>
       <c r="E91">
-        <v>9.684999999999995</v>
+        <v>10.15</v>
       </c>
       <c r="F91">
-        <v>41.385</v>
+        <v>41.85</v>
       </c>
       <c r="G91">
         <v>15.1</v>
@@ -8743,28 +8743,28 @@
         <v>17.196</v>
       </c>
       <c r="M91">
-        <v>2.2140975</v>
+        <v>2.238975</v>
       </c>
       <c r="N91">
-        <v>14.9819025</v>
+        <v>14.957025</v>
       </c>
       <c r="O91">
-        <v>3.745475625000001</v>
+        <v>3.73925625</v>
       </c>
       <c r="P91">
-        <v>11.236426875</v>
+        <v>11.21776875</v>
       </c>
       <c r="Q91">
-        <v>11.290426875</v>
+        <v>11.27176875</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.002015906426867</v>
+        <v>1.094255382931067</v>
       </c>
       <c r="T91">
-        <v>13.91410655215708</v>
+        <v>15.25630332567706</v>
       </c>
       <c r="U91">
         <v>0.0535</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>7.766595644500752</v>
+        <v>7.680300137339632</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1455380382931066</v>
+        <v>0.1456890768792579</v>
       </c>
       <c r="C92">
-        <v>6.933908103291749</v>
+        <v>6.449628848599829</v>
       </c>
       <c r="D92">
-        <v>33.68390810329175</v>
+        <v>33.66462884859983</v>
       </c>
       <c r="E92">
-        <v>10.15</v>
+        <v>10.615</v>
       </c>
       <c r="F92">
-        <v>41.85</v>
+        <v>42.315</v>
       </c>
       <c r="G92">
         <v>15.1</v>
@@ -8825,45 +8825,45 @@
         <v>17.196</v>
       </c>
       <c r="M92">
-        <v>2.238975</v>
+        <v>2.2977045</v>
       </c>
       <c r="N92">
-        <v>14.957025</v>
+        <v>14.8982955</v>
       </c>
       <c r="O92">
-        <v>3.73925625</v>
+        <v>3.724573875</v>
       </c>
       <c r="P92">
-        <v>11.21776875</v>
+        <v>11.173721625</v>
       </c>
       <c r="Q92">
-        <v>11.27176875</v>
+        <v>11.227721625</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.094255382931067</v>
+        <v>1.206992520880644</v>
       </c>
       <c r="T92">
-        <v>15.25630332567706</v>
+        <v>16.89676604886814</v>
       </c>
       <c r="U92">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V92">
         <v>0.25</v>
       </c>
       <c r="W92">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y92">
-        <v>7.680300137339632</v>
+        <v>7.483991087626802</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1456890768792579</v>
+        <v>0.1453001154654092</v>
       </c>
       <c r="C93">
-        <v>6.449628848599829</v>
+        <v>6.034322488895974</v>
       </c>
       <c r="D93">
-        <v>33.66462884859983</v>
+        <v>33.71432248889597</v>
       </c>
       <c r="E93">
-        <v>10.615</v>
+        <v>11.08</v>
       </c>
       <c r="F93">
-        <v>42.315</v>
+        <v>42.78</v>
       </c>
       <c r="G93">
         <v>15.1</v>
@@ -8907,28 +8907,28 @@
         <v>17.196</v>
       </c>
       <c r="M93">
-        <v>2.2977045</v>
+        <v>2.322954</v>
       </c>
       <c r="N93">
-        <v>14.8982955</v>
+        <v>14.873046</v>
       </c>
       <c r="O93">
-        <v>3.724573875</v>
+        <v>3.718261500000001</v>
       </c>
       <c r="P93">
-        <v>11.173721625</v>
+        <v>11.1547845</v>
       </c>
       <c r="Q93">
-        <v>11.227721625</v>
+        <v>11.2087845</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.206992520880644</v>
+        <v>1.347913943317615</v>
       </c>
       <c r="T93">
-        <v>16.89676604886814</v>
+        <v>18.947344452857</v>
       </c>
       <c r="U93">
         <v>0.0543</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>7.483991087626802</v>
+        <v>7.402643358413469</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1453001154654092</v>
+        <v>0.1449111540515604</v>
       </c>
       <c r="C94">
-        <v>6.034322488895974</v>
+        <v>5.619163055424188</v>
       </c>
       <c r="D94">
-        <v>33.71432248889597</v>
+        <v>33.76416305542419</v>
       </c>
       <c r="E94">
-        <v>11.08</v>
+        <v>11.545</v>
       </c>
       <c r="F94">
-        <v>42.78</v>
+        <v>43.245</v>
       </c>
       <c r="G94">
         <v>15.1</v>
@@ -8989,28 +8989,28 @@
         <v>17.196</v>
       </c>
       <c r="M94">
-        <v>2.322954</v>
+        <v>2.3482035</v>
       </c>
       <c r="N94">
-        <v>14.873046</v>
+        <v>14.8477965</v>
       </c>
       <c r="O94">
-        <v>3.718261500000001</v>
+        <v>3.711949125</v>
       </c>
       <c r="P94">
-        <v>11.1547845</v>
+        <v>11.135847375</v>
       </c>
       <c r="Q94">
-        <v>11.2087845</v>
+        <v>11.189847375</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.347913943317615</v>
+        <v>1.529098629308007</v>
       </c>
       <c r="T94">
-        <v>18.947344452857</v>
+        <v>21.58380240084267</v>
       </c>
       <c r="U94">
         <v>0.0543</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>7.402643358413469</v>
+        <v>7.323045042731603</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1449111540515604</v>
+        <v>0.1445221926377117</v>
       </c>
       <c r="C95">
-        <v>5.619163055424188</v>
+        <v>5.204151200761302</v>
       </c>
       <c r="D95">
-        <v>33.76416305542419</v>
+        <v>33.8141512007613</v>
       </c>
       <c r="E95">
-        <v>11.545</v>
+        <v>12.01</v>
       </c>
       <c r="F95">
-        <v>43.245</v>
+        <v>43.71</v>
       </c>
       <c r="G95">
         <v>15.1</v>
@@ -9071,28 +9071,28 @@
         <v>17.196</v>
       </c>
       <c r="M95">
-        <v>2.3482035</v>
+        <v>2.373453</v>
       </c>
       <c r="N95">
-        <v>14.8477965</v>
+        <v>14.822547</v>
       </c>
       <c r="O95">
-        <v>3.711949125</v>
+        <v>3.70563675</v>
       </c>
       <c r="P95">
-        <v>11.135847375</v>
+        <v>11.11691025</v>
       </c>
       <c r="Q95">
-        <v>11.189847375</v>
+        <v>11.17091025</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.529098629308007</v>
+        <v>1.77067821062853</v>
       </c>
       <c r="T95">
-        <v>21.58380240084267</v>
+        <v>25.09907966482356</v>
       </c>
       <c r="U95">
         <v>0.0543</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>7.323045042731603</v>
+        <v>7.245140308234459</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1445221926377117</v>
+        <v>0.144133231223863</v>
       </c>
       <c r="C96">
-        <v>5.204151200761302</v>
+        <v>4.789287581354394</v>
       </c>
       <c r="D96">
-        <v>33.8141512007613</v>
+        <v>33.8642875813544</v>
       </c>
       <c r="E96">
-        <v>12.01</v>
+        <v>12.475</v>
       </c>
       <c r="F96">
-        <v>43.71</v>
+        <v>44.175</v>
       </c>
       <c r="G96">
         <v>15.1</v>
@@ -9153,28 +9153,28 @@
         <v>17.196</v>
       </c>
       <c r="M96">
-        <v>2.373453</v>
+        <v>2.3987025</v>
       </c>
       <c r="N96">
-        <v>14.822547</v>
+        <v>14.7972975</v>
       </c>
       <c r="O96">
-        <v>3.70563675</v>
+        <v>3.699324375</v>
       </c>
       <c r="P96">
-        <v>11.11691025</v>
+        <v>11.097973125</v>
       </c>
       <c r="Q96">
-        <v>11.17091025</v>
+        <v>11.151973125</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.77067821062853</v>
+        <v>2.108889624477262</v>
       </c>
       <c r="T96">
-        <v>25.09907966482356</v>
+        <v>30.02046783439683</v>
       </c>
       <c r="U96">
         <v>0.0543</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>7.245140308234459</v>
+        <v>7.168875673410938</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.144133231223863</v>
+        <v>0.1437442698100142</v>
       </c>
       <c r="C97">
-        <v>4.789287581354394</v>
+        <v>4.374572857549651</v>
       </c>
       <c r="D97">
-        <v>33.8642875813544</v>
+        <v>33.91457285754965</v>
       </c>
       <c r="E97">
-        <v>12.475</v>
+        <v>12.94</v>
       </c>
       <c r="F97">
-        <v>44.175</v>
+        <v>44.64</v>
       </c>
       <c r="G97">
         <v>15.1</v>
@@ -9235,28 +9235,28 @@
         <v>17.196</v>
       </c>
       <c r="M97">
-        <v>2.3987025</v>
+        <v>2.423952</v>
       </c>
       <c r="N97">
-        <v>14.7972975</v>
+        <v>14.772048</v>
       </c>
       <c r="O97">
-        <v>3.699324375</v>
+        <v>3.693012</v>
       </c>
       <c r="P97">
-        <v>11.097973125</v>
+        <v>11.079036</v>
       </c>
       <c r="Q97">
-        <v>11.151973125</v>
+        <v>11.133036</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.108889624477262</v>
+        <v>2.616206745250361</v>
       </c>
       <c r="T97">
-        <v>30.02046783439683</v>
+        <v>37.40255008875672</v>
       </c>
       <c r="U97">
         <v>0.0543</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>7.168875673410938</v>
+        <v>7.094199885146241</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1437442698100143</v>
+        <v>0.1433553083961655</v>
       </c>
       <c r="C98">
-        <v>4.374572857549644</v>
+        <v>3.960007693621272</v>
       </c>
       <c r="D98">
-        <v>33.91457285754964</v>
+        <v>33.96500769362127</v>
       </c>
       <c r="E98">
-        <v>12.94</v>
+        <v>13.40499999999999</v>
       </c>
       <c r="F98">
-        <v>44.64</v>
+        <v>45.105</v>
       </c>
       <c r="G98">
         <v>15.1</v>
@@ -9317,28 +9317,28 @@
         <v>17.196</v>
       </c>
       <c r="M98">
-        <v>2.423952</v>
+        <v>2.4492015</v>
       </c>
       <c r="N98">
-        <v>14.772048</v>
+        <v>14.7467985</v>
       </c>
       <c r="O98">
-        <v>3.693012</v>
+        <v>3.686699625</v>
       </c>
       <c r="P98">
-        <v>11.079036</v>
+        <v>11.060098875</v>
       </c>
       <c r="Q98">
-        <v>11.133036</v>
+        <v>11.114098875</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.616206745250354</v>
+        <v>3.461735279872181</v>
       </c>
       <c r="T98">
-        <v>37.40255008875663</v>
+        <v>49.70602051268972</v>
       </c>
       <c r="U98">
         <v>0.0543</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>7.094199885146241</v>
+        <v>7.021063803856073</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1433553083961655</v>
+        <v>0.1429663469823168</v>
       </c>
       <c r="C99">
-        <v>3.960007693621272</v>
+        <v>3.54559275780074</v>
       </c>
       <c r="D99">
-        <v>33.96500769362127</v>
+        <v>34.01559275780074</v>
       </c>
       <c r="E99">
-        <v>13.40499999999999</v>
+        <v>13.87</v>
       </c>
       <c r="F99">
-        <v>45.105</v>
+        <v>45.57</v>
       </c>
       <c r="G99">
         <v>15.1</v>
@@ -9399,28 +9399,28 @@
         <v>17.196</v>
       </c>
       <c r="M99">
-        <v>2.4492015</v>
+        <v>2.474451</v>
       </c>
       <c r="N99">
-        <v>14.7467985</v>
+        <v>14.721549</v>
       </c>
       <c r="O99">
-        <v>3.686699625</v>
+        <v>3.68038725</v>
       </c>
       <c r="P99">
-        <v>11.060098875</v>
+        <v>11.04116175</v>
       </c>
       <c r="Q99">
-        <v>11.114098875</v>
+        <v>11.09516175</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.461735279872181</v>
+        <v>5.152792349115835</v>
       </c>
       <c r="T99">
-        <v>49.70602051268972</v>
+        <v>74.31296136055592</v>
       </c>
       <c r="U99">
         <v>0.0543</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>7.021063803856073</v>
+        <v>6.94942029565346</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1429663469823168</v>
+        <v>0.1425773855684681</v>
       </c>
       <c r="C100">
-        <v>3.54559275780074</v>
+        <v>3.131328722306371</v>
       </c>
       <c r="D100">
-        <v>34.01559275780074</v>
+        <v>34.06632872230637</v>
       </c>
       <c r="E100">
-        <v>13.87</v>
+        <v>14.33499999999999</v>
       </c>
       <c r="F100">
-        <v>45.57</v>
+        <v>46.035</v>
       </c>
       <c r="G100">
         <v>15.1</v>
@@ -9481,28 +9481,28 @@
         <v>17.196</v>
       </c>
       <c r="M100">
-        <v>2.474451</v>
+        <v>2.4997005</v>
       </c>
       <c r="N100">
-        <v>14.721549</v>
+        <v>14.6962995</v>
       </c>
       <c r="O100">
-        <v>3.68038725</v>
+        <v>3.674074875000001</v>
       </c>
       <c r="P100">
-        <v>11.04116175</v>
+        <v>11.022224625</v>
       </c>
       <c r="Q100">
-        <v>11.09516175</v>
+        <v>11.076224625</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.152792349115835</v>
+        <v>10.2259635568468</v>
       </c>
       <c r="T100">
-        <v>74.31296136055592</v>
+        <v>148.1337839041545</v>
       </c>
       <c r="U100">
         <v>0.0543</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>6.94942029565346</v>
+        <v>6.879224131050901</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1425773855684681</v>
-      </c>
-      <c r="C101">
-        <v>3.131328722306371</v>
-      </c>
-      <c r="D101">
-        <v>34.06632872230637</v>
-      </c>
-      <c r="E101">
-        <v>14.33499999999999</v>
-      </c>
-      <c r="F101">
-        <v>46.035</v>
-      </c>
-      <c r="G101">
-        <v>15.1</v>
-      </c>
-      <c r="H101">
-        <v>14.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>17.25</v>
-      </c>
-      <c r="K101">
-        <v>0.054</v>
-      </c>
-      <c r="L101">
-        <v>17.196</v>
-      </c>
-      <c r="M101">
-        <v>2.4997005</v>
-      </c>
-      <c r="N101">
-        <v>14.6962995</v>
-      </c>
-      <c r="O101">
-        <v>3.674074875000001</v>
-      </c>
-      <c r="P101">
-        <v>11.022224625</v>
-      </c>
-      <c r="Q101">
-        <v>11.076224625</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.2259635568468</v>
-      </c>
-      <c r="T101">
-        <v>148.1337839041545</v>
-      </c>
-      <c r="U101">
-        <v>0.0543</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.040725</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A2/A</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>6.879224131050901</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
